--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057D026F-8E9C-43DE-8B5B-F1F960304140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1139150A-C44D-4496-A02C-83C3C6D9C179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="23" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="891">
   <si>
     <t>REAL BETIS</t>
   </si>
@@ -3178,7 +3178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3391,8 +3391,11 @@
     <xf numFmtId="0" fontId="16" fillId="49" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="48" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="46" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3405,6 +3408,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3458,11 +3464,8 @@
     <xf numFmtId="0" fontId="6" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="48" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="46" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3774,15 +3777,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3816,11 +3819,11 @@
       </c>
       <c r="C3" s="4">
         <f>COUNTIF('D. ALAVÉS'!C3:C25,"")</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5">
         <f>COUNTIF('D. ALAVÉS'!D3:D25,"X")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" s="6">
         <f>SUMIF('D. ALAVÉS'!E3:E25,"&gt;"&amp;0,'D. ALAVÉS'!E3:E25)</f>
@@ -3828,11 +3831,11 @@
       </c>
       <c r="F3" s="7">
         <f>SUM('D. ALAVÉS'!F3:F25)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="8">
         <f>SUM('D. ALAVÉS'!G3:G25)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3872,11 +3875,11 @@
       </c>
       <c r="C5" s="4">
         <f>COUNTIF('ATLÉTICO DE MADRID'!C3:C26,"")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5">
         <f>COUNTIF('ATLÉTICO DE MADRID'!D3:D26,"X")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="6">
         <f>SUMIF('ATLÉTICO DE MADRID'!E3:E26,"&gt;"&amp;0,'ATLÉTICO DE MADRID'!E3:E26)</f>
@@ -3928,11 +3931,11 @@
       </c>
       <c r="C7" s="4">
         <f>COUNTIF('REAL BETIS'!C3:C25,"")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" s="5">
         <f>COUNTIF('REAL BETIS'!D3:D25,"X")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" s="6">
         <f>SUMIF('REAL BETIS'!E3:E25,"&gt;"&amp;0,'REAL BETIS'!E3:E25)</f>
@@ -3956,11 +3959,11 @@
       </c>
       <c r="C8" s="4">
         <f>COUNTIF('RC CELTA DE VIGO'!C3:C26,"")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5">
         <f>COUNTIF('RC CELTA DE VIGO'!D3:D26,"X")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" s="6">
         <f>SUMIF('RC CELTA DE VIGO'!E3:E26,"&gt;"&amp;0,'RC CELTA DE VIGO'!E3:E26)</f>
@@ -3984,11 +3987,11 @@
       </c>
       <c r="C9" s="4">
         <f>COUNTIF('RC DEPORTIVO'!C3:C25,"")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5">
         <f>COUNTIF('RC DEPORTIVO'!D3:D25,"X")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
         <f>SUMIF('RC DEPORTIVO'!E3:E25,"&gt;"&amp;0,'RC DEPORTIVO'!E3:E25)</f>
@@ -4012,15 +4015,15 @@
       </c>
       <c r="C10" s="4">
         <f>COUNTIF('ELCHE CF'!C3:C25,"")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5">
         <f>COUNTIF('ELCHE CF'!D3:D25,"X")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6">
         <f>SUMIF('ELCHE CF'!E3:E25,"&gt;"&amp;0,'ELCHE CF'!E3:E25)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="7">
         <f>SUM('ELCHE CF'!F3:F25)</f>
@@ -4028,7 +4031,7 @@
       </c>
       <c r="G10" s="8">
         <f>SUM('ELCHE CF'!G3:G25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4040,15 +4043,15 @@
       </c>
       <c r="C11" s="4">
         <f>COUNTIF('RCD ESPANYOL'!C3:C25,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5">
         <f>COUNTIF('RCD ESPANYOL'!D3:D25,"X")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="6">
         <f>SUMIF('RCD ESPANYOL'!E3:E25,"&gt;"&amp;0,'RCD ESPANYOL'!E3:E25)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="7">
         <f>SUM('RCD ESPANYOL'!F3:F25)</f>
@@ -4056,7 +4059,7 @@
       </c>
       <c r="G11" s="8">
         <f>SUM('RCD ESPANYOL'!G3:G25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4068,15 +4071,15 @@
       </c>
       <c r="C12" s="4">
         <f>COUNTIF('GETAFE CF'!C3:C23,"")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5">
         <f>COUNTIF('GETAFE CF'!D3:D23,"X")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="6">
         <f>SUMIF('GETAFE CF'!E3:E23,"&gt;"&amp;0,'GETAFE CF'!E3:E23)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="7">
         <f>SUM('GETAFE CF'!F3:F23)</f>
@@ -4084,7 +4087,7 @@
       </c>
       <c r="G12" s="8">
         <f>SUM('GETAFE CF'!G3:G23)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4096,11 +4099,11 @@
       </c>
       <c r="C13" s="4">
         <f>COUNTIF('LEVANTE UD'!C3:C26,"")</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13" s="5">
         <f>COUNTIF('LEVANTE UD'!D3:D26,"X")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6">
         <f>SUMIF('LEVANTE UD'!E3:E26,"&gt;"&amp;0,'LEVANTE UD'!E3:E26)</f>
@@ -4124,11 +4127,11 @@
       </c>
       <c r="C14" s="4">
         <f>COUNTIF('REAL MADRID CF'!C3:C27,"")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5">
         <f>COUNTIF('REAL MADRID CF'!D3:D27,"X")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="6">
         <f>SUMIF('REAL MADRID CF'!E3:E27,"&gt;"&amp;0,'REAL MADRID CF'!E3:E27)</f>
@@ -4152,11 +4155,11 @@
       </c>
       <c r="C15" s="4">
         <f>COUNTIF('MÁLAGA CF'!C3:C24,"")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5">
         <f>COUNTIF('MÁLAGA CF'!D3:D24,"X")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6">
         <f>SUMIF('MÁLAGA CF'!E3:E24,"&gt;"&amp;0,'MÁLAGA CF'!E3:E24)</f>
@@ -4180,11 +4183,11 @@
       </c>
       <c r="C16" s="4">
         <f>COUNTIF('CA OSASUNA'!C3:C25,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5">
         <f>COUNTIF('CA OSASUNA'!D3:D25,"X")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="6">
         <f>SUMIF('CA OSASUNA'!E3:E25,"&gt;"&amp;0,'CA OSASUNA'!E3:E25)</f>
@@ -4208,11 +4211,11 @@
       </c>
       <c r="C17" s="4">
         <f>COUNTIF('R. RACING CLUB'!C3:C27,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5">
         <f>COUNTIF('R. RACING CLUB'!D3:D27,"X")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6">
         <f>SUMIF('R. RACING CLUB'!E3:E27,"&gt;"&amp;0,'R. RACING CLUB'!E3:E27)</f>
@@ -4236,11 +4239,11 @@
       </c>
       <c r="C18" s="4">
         <f>COUNTIF('RAYO VALLECANO'!C3:C25,"")</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D18" s="5">
         <f>COUNTIF('RAYO VALLECANO'!D3:D25,"X")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="6">
         <f>SUMIF('RAYO VALLECANO'!E3:E25,"&gt;"&amp;0,'RAYO VALLECANO'!E3:E25)</f>
@@ -4264,11 +4267,11 @@
       </c>
       <c r="C19" s="4">
         <f>COUNTIF('REAL SOCIEDAD'!C3:C23,"")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5">
         <f>COUNTIF('REAL SOCIEDAD'!D3:D23,"X")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6">
         <f>SUMIF('REAL SOCIEDAD'!E3:E23,"&gt;"&amp;0,'REAL SOCIEDAD'!E3:E23)</f>
@@ -4292,11 +4295,11 @@
       </c>
       <c r="C20" s="4">
         <f>COUNTIF('SEVILLA FC'!C3:C26,"")</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D20" s="5">
         <f>COUNTIF('SEVILLA FC'!D3:D26,"X")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="6">
         <f>SUMIF('SEVILLA FC'!E3:E26,"&gt;"&amp;0,'SEVILLA FC'!E3:E26)</f>
@@ -4320,11 +4323,11 @@
       </c>
       <c r="C21" s="4">
         <f>COUNTIF('VALENCIA CF'!C3:C26,"")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" s="5">
         <f>COUNTIF('VALENCIA CF'!D3:D26,"X")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6">
         <f>SUMIF('VALENCIA CF'!E3:E26,"&gt;"&amp;0,'VALENCIA CF'!E3:E26)</f>
@@ -4348,15 +4351,15 @@
       </c>
       <c r="C22" s="4">
         <f>COUNTIF('VILLARREAL CF'!C3:C26,"")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D22" s="5">
         <f>COUNTIF('VILLARREAL CF'!D3:D26,"X")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6">
         <f>SUMIF('VILLARREAL CF'!E3:E26,"&gt;"&amp;0,'VILLARREAL CF'!E3:E26)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="7">
         <f>SUM('VILLARREAL CF'!F3:F26)</f>
@@ -4364,7 +4367,7 @@
       </c>
       <c r="G22" s="8">
         <f>SUM('VILLARREAL CF'!G3:G26)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4376,11 +4379,11 @@
       </c>
       <c r="C23" s="4">
         <f>COUNTIF('ADN - LALIGA PRIME'!C3:C17,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5">
         <f>COUNTIF('ADN - LALIGA PRIME'!D3:D17,"X")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6">
         <f>SUMIF('ADN - LALIGA PRIME'!E3:E17,"&gt;"&amp;0,'ADN - LALIGA PRIME'!E3:E17)</f>
@@ -4404,11 +4407,11 @@
       </c>
       <c r="C24" s="4">
         <f>COUNTIF('LALIGA FANTASY'!C3:C11,"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5">
         <f>COUNTIF('LALIGA FANTASY'!D3:D11,"X")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="6">
         <f>SUMIF('LALIGA FANTASY'!E3:E11,"&gt;"&amp;0,'LALIGA FANTASY'!E3:E11)</f>
@@ -4432,11 +4435,11 @@
       </c>
       <c r="C25" s="4">
         <f>COUNTIF('DRAFT 23'!C3:C25,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="5">
         <f>COUNTIF('DRAFT 23'!D3:D25,"X")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6">
         <f>SUMIF('DRAFT 23'!E3:E25,"&gt;"&amp;0,'DRAFT 23'!E3:E25)</f>
@@ -4460,11 +4463,11 @@
       </c>
       <c r="C26" s="4">
         <f>COUNTIF('DRAFT 23 KROMIX'!C3:C25,"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" s="5">
         <f>COUNTIF('DRAFT 23 KROMIX'!D3:D25,"X")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6">
         <f>SUMIF('DRAFT 23 KROMIX'!E3:E25,"&gt;"&amp;0,'DRAFT 23 KROMIX'!E3:E25)</f>
@@ -4516,11 +4519,11 @@
       </c>
       <c r="C28" s="4">
         <f>COUNTIF('CHICLE LIGA 2627'!C3:C82,"")</f>
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D28" s="5">
         <f>COUNTIF('CHICLE LIGA 2627'!D3:D82,"X")</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E28" s="6">
         <f>SUMIF('CHICLE LIGA 2627'!E3:E82,"&gt;"&amp;0,'CHICLE LIGA 2627'!E3:E82)</f>
@@ -4544,11 +4547,11 @@
       </c>
       <c r="C29" s="29">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!C3:C42,"")</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D29" s="30">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!D3:D42,"X")</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E29" s="31">
         <f>SUMIF('ÚLTIMOS FICHAJES'!E3:E42,"&gt;"&amp;0,'ÚLTIMOS FICHAJES'!E3:E42)</f>
@@ -4573,33 +4576,33 @@
       </c>
       <c r="C30" s="13">
         <f t="shared" si="0"/>
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="0"/>
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="E30" s="15">
         <f t="shared" si="0"/>
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
@@ -4629,15 +4632,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4790,7 +4793,7 @@
         <v>271</v>
       </c>
       <c r="C9" s="60"/>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="62"/>
@@ -4872,7 +4875,7 @@
         <v>276</v>
       </c>
       <c r="C13" s="60"/>
-      <c r="D13" s="95" t="s">
+      <c r="D13" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="62"/>
@@ -4889,10 +4892,10 @@
       <c r="B14" s="66" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C14" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="61"/>
       <c r="E14" s="62">
         <v>1</v>
       </c>
@@ -4916,14 +4919,14 @@
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="63">
         <v>1</v>
       </c>
       <c r="G15" s="64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5142,15 +5145,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5220,10 +5223,10 @@
       <c r="B5" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="61"/>
       <c r="E5" s="62"/>
       <c r="F5" s="63"/>
       <c r="G5" s="64">
@@ -5340,11 +5343,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="61"/>
-      <c r="E11" s="62"/>
+      <c r="E11" s="62">
+        <v>1</v>
+      </c>
       <c r="F11" s="63"/>
       <c r="G11" s="64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5543,7 +5548,7 @@
         <v>308</v>
       </c>
       <c r="C22" s="60"/>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="62"/>
@@ -5593,15 +5598,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5633,10 +5638,10 @@
       <c r="B3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C3" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="61"/>
       <c r="E3" s="62"/>
       <c r="F3" s="63"/>
       <c r="G3" s="64">
@@ -5748,7 +5753,7 @@
         <v>315</v>
       </c>
       <c r="C9" s="60"/>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="62"/>
@@ -5765,10 +5770,10 @@
       <c r="B10" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C10" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="61"/>
       <c r="E10" s="62"/>
       <c r="F10" s="63"/>
       <c r="G10" s="64">
@@ -5783,10 +5788,10 @@
       <c r="B11" s="59" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C11" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="72"/>
       <c r="E11" s="62">
         <v>2</v>
       </c>
@@ -5990,7 +5995,7 @@
         <v>327</v>
       </c>
       <c r="C21" s="60"/>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="62"/>
@@ -6085,10 +6090,10 @@
       <c r="B26" s="66" t="s">
         <v>332</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C26" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="61"/>
       <c r="E26" s="62"/>
       <c r="F26" s="63"/>
       <c r="G26" s="64">
@@ -6118,15 +6123,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6424,10 +6429,10 @@
       <c r="B16" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="61"/>
       <c r="E16" s="62">
         <v>1</v>
       </c>
@@ -6468,10 +6473,10 @@
       <c r="B18" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C18" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="61"/>
       <c r="E18" s="62">
         <v>1</v>
       </c>
@@ -6595,7 +6600,7 @@
         <v>361</v>
       </c>
       <c r="C24" s="60"/>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="62"/>
@@ -6693,15 +6698,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6869,10 +6874,10 @@
       <c r="B10" s="66" t="s">
         <v>371</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C10" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="61"/>
       <c r="E10" s="62">
         <v>3</v>
       </c>
@@ -6989,10 +6994,10 @@
       <c r="B16" s="66" t="s">
         <v>377</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="61"/>
       <c r="E16" s="62">
         <v>2</v>
       </c>
@@ -7053,10 +7058,10 @@
       <c r="B19" s="59" t="s">
         <v>380</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C19" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="61"/>
       <c r="E19" s="62"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64">
@@ -7188,15 +7193,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -7464,10 +7469,10 @@
       <c r="B15" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C15" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="61"/>
       <c r="E15" s="62"/>
       <c r="F15" s="63"/>
       <c r="G15" s="64">
@@ -7577,7 +7582,7 @@
         <v>403</v>
       </c>
       <c r="C21" s="60"/>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="62"/>
@@ -7689,15 +7694,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -7838,7 +7843,7 @@
         <v>413</v>
       </c>
       <c r="C9" s="60"/>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="62"/>
@@ -7894,7 +7899,7 @@
         <v>416</v>
       </c>
       <c r="C12" s="60"/>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="62"/>
@@ -7911,10 +7916,10 @@
       <c r="B13" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C13" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="61"/>
       <c r="E13" s="62">
         <v>2</v>
       </c>
@@ -8100,7 +8105,7 @@
         <v>426</v>
       </c>
       <c r="C22" s="60"/>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="62"/>
@@ -8230,15 +8235,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -8411,7 +8416,7 @@
         <v>438</v>
       </c>
       <c r="C10" s="60"/>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="62">
@@ -8493,7 +8498,7 @@
         <v>442</v>
       </c>
       <c r="C14" s="60"/>
-      <c r="D14" s="95" t="s">
+      <c r="D14" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="62"/>
@@ -8570,10 +8575,10 @@
       <c r="B18" s="66" t="s">
         <v>448</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C18" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="61"/>
       <c r="E18" s="62"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64">
@@ -8624,10 +8629,10 @@
       <c r="B21" s="59" t="s">
         <v>451</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C21" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="61"/>
       <c r="E21" s="62"/>
       <c r="F21" s="63"/>
       <c r="G21" s="64">
@@ -8642,10 +8647,10 @@
       <c r="B22" s="66" t="s">
         <v>452</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C22" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="61"/>
       <c r="E22" s="62"/>
       <c r="F22" s="63"/>
       <c r="G22" s="64">
@@ -8733,15 +8738,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -8809,10 +8814,10 @@
       <c r="B5" s="35" t="s">
         <v>457</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="44"/>
       <c r="E5" s="45"/>
       <c r="F5" s="46"/>
       <c r="G5" s="40">
@@ -8907,10 +8912,10 @@
       <c r="B10" s="42" t="s">
         <v>462</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44" t="s">
-        <v>10</v>
-      </c>
+      <c r="C10" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="44"/>
       <c r="E10" s="45"/>
       <c r="F10" s="46"/>
       <c r="G10" s="40">
@@ -9151,10 +9156,10 @@
       <c r="B23" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="44" t="s">
-        <v>10</v>
-      </c>
+      <c r="C23" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="44"/>
       <c r="E23" s="45"/>
       <c r="F23" s="46"/>
       <c r="G23" s="40">
@@ -9184,15 +9189,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9246,10 +9251,10 @@
       <c r="B4" s="66" t="s">
         <v>476</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="61"/>
       <c r="E4" s="62"/>
       <c r="F4" s="63"/>
       <c r="G4" s="64">
@@ -9338,10 +9343,10 @@
       <c r="B9" s="59" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="95" t="s">
-        <v>10</v>
-      </c>
+      <c r="C9" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="72"/>
       <c r="E9" s="62"/>
       <c r="F9" s="63"/>
       <c r="G9" s="64">
@@ -9395,7 +9400,7 @@
         <v>484</v>
       </c>
       <c r="C12" s="60"/>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="62"/>
@@ -9514,10 +9519,10 @@
       <c r="B18" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C18" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="61"/>
       <c r="E18" s="71">
         <v>2</v>
       </c>
@@ -9556,10 +9561,10 @@
       <c r="B20" s="66" t="s">
         <v>492</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C20" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="61"/>
       <c r="E20" s="62"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64">
@@ -9657,7 +9662,7 @@
         <v>497</v>
       </c>
       <c r="C25" s="60"/>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="62"/>
@@ -9711,15 +9716,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9814,7 +9819,7 @@
         <v>89</v>
       </c>
       <c r="C6" s="60"/>
-      <c r="D6" s="95" t="s">
+      <c r="D6" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="62"/>
@@ -9867,10 +9872,10 @@
       <c r="B9" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C9" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="61"/>
       <c r="E9" s="62"/>
       <c r="F9" s="63"/>
       <c r="G9" s="64">
@@ -9902,7 +9907,7 @@
         <v>96</v>
       </c>
       <c r="C11" s="60"/>
-      <c r="D11" s="95" t="s">
+      <c r="D11" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="62"/>
@@ -9938,7 +9943,7 @@
         <v>98</v>
       </c>
       <c r="C13" s="60"/>
-      <c r="D13" s="95" t="s">
+      <c r="D13" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="62"/>
@@ -9955,10 +9960,10 @@
       <c r="B14" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C14" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="61"/>
       <c r="E14" s="62">
         <v>1</v>
       </c>
@@ -9999,10 +10004,10 @@
       <c r="B16" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="61"/>
       <c r="E16" s="62"/>
       <c r="F16" s="63"/>
       <c r="G16" s="64">
@@ -10107,11 +10112,11 @@
         <v>2</v>
       </c>
       <c r="F21" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10139,10 +10144,10 @@
       <c r="B23" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C23" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="61"/>
       <c r="E23" s="62">
         <v>2</v>
       </c>
@@ -10214,15 +10219,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -10622,10 +10627,10 @@
       <c r="B22" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C22" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="37"/>
       <c r="E22" s="38"/>
       <c r="F22" s="39"/>
       <c r="G22" s="40">
@@ -10656,10 +10661,10 @@
       <c r="B24" s="53" t="s">
         <v>519</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C24" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="37"/>
       <c r="E24" s="38"/>
       <c r="F24" s="39"/>
       <c r="G24" s="40">
@@ -10731,15 +10736,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -10797,11 +10802,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
+      <c r="E4" s="38">
+        <v>1</v>
+      </c>
       <c r="F4" s="39"/>
       <c r="G4" s="40">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10849,10 +10856,10 @@
       <c r="B7" s="35" t="s">
         <v>527</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C7" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="37"/>
       <c r="E7" s="38"/>
       <c r="F7" s="39"/>
       <c r="G7" s="40">
@@ -11017,10 +11024,10 @@
       <c r="B16" s="42" t="s">
         <v>538</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="37"/>
       <c r="E16" s="38"/>
       <c r="F16" s="39"/>
       <c r="G16" s="40">
@@ -11053,10 +11060,10 @@
       <c r="B18" s="42" t="s">
         <v>540</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C18" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="37"/>
       <c r="E18" s="38"/>
       <c r="F18" s="39"/>
       <c r="G18" s="40">
@@ -11240,15 +11247,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="90" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
@@ -11280,10 +11287,10 @@
       <c r="B3" s="59" t="s">
         <v>551</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C3" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="61"/>
       <c r="E3" s="62"/>
       <c r="F3" s="63"/>
       <c r="G3" s="64">
@@ -11532,10 +11539,10 @@
       <c r="B17" s="59" t="s">
         <v>579</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C17" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="61"/>
       <c r="E17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="64">
@@ -11641,7 +11648,7 @@
         <v>591</v>
       </c>
       <c r="C23" s="60"/>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="62"/>
@@ -11659,7 +11666,7 @@
         <v>593</v>
       </c>
       <c r="C24" s="60"/>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="62"/>
@@ -11677,7 +11684,7 @@
         <v>595</v>
       </c>
       <c r="C25" s="60"/>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="62"/>
@@ -11695,7 +11702,7 @@
         <v>597</v>
       </c>
       <c r="C26" s="60"/>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="62"/>
@@ -11713,7 +11720,7 @@
         <v>599</v>
       </c>
       <c r="C27" s="60"/>
-      <c r="D27" s="95" t="s">
+      <c r="D27" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="62"/>
@@ -11731,7 +11738,7 @@
         <v>601</v>
       </c>
       <c r="C28" s="60"/>
-      <c r="D28" s="95" t="s">
+      <c r="D28" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="62"/>
@@ -11749,7 +11756,7 @@
         <v>603</v>
       </c>
       <c r="C29" s="60"/>
-      <c r="D29" s="95" t="s">
+      <c r="D29" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="62"/>
@@ -11767,7 +11774,7 @@
         <v>605</v>
       </c>
       <c r="C30" s="60"/>
-      <c r="D30" s="95" t="s">
+      <c r="D30" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="62"/>
@@ -11785,7 +11792,7 @@
         <v>607</v>
       </c>
       <c r="C31" s="60"/>
-      <c r="D31" s="95" t="s">
+      <c r="D31" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="62"/>
@@ -11803,7 +11810,7 @@
         <v>609</v>
       </c>
       <c r="C32" s="60"/>
-      <c r="D32" s="95" t="s">
+      <c r="D32" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="62"/>
@@ -11821,7 +11828,7 @@
         <v>611</v>
       </c>
       <c r="C33" s="60"/>
-      <c r="D33" s="95" t="s">
+      <c r="D33" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="62"/>
@@ -11839,7 +11846,7 @@
         <v>613</v>
       </c>
       <c r="C34" s="60"/>
-      <c r="D34" s="95" t="s">
+      <c r="D34" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="62"/>
@@ -11857,7 +11864,7 @@
         <v>615</v>
       </c>
       <c r="C35" s="60"/>
-      <c r="D35" s="95" t="s">
+      <c r="D35" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="62"/>
@@ -11875,7 +11882,7 @@
         <v>617</v>
       </c>
       <c r="C36" s="60"/>
-      <c r="D36" s="95" t="s">
+      <c r="D36" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="62"/>
@@ -11893,7 +11900,7 @@
         <v>619</v>
       </c>
       <c r="C37" s="60"/>
-      <c r="D37" s="95" t="s">
+      <c r="D37" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="62"/>
@@ -11911,7 +11918,7 @@
         <v>621</v>
       </c>
       <c r="C38" s="60"/>
-      <c r="D38" s="95" t="s">
+      <c r="D38" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="62"/>
@@ -11929,7 +11936,7 @@
         <v>623</v>
       </c>
       <c r="C39" s="60"/>
-      <c r="D39" s="95" t="s">
+      <c r="D39" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="62"/>
@@ -11947,7 +11954,7 @@
         <v>625</v>
       </c>
       <c r="C40" s="60"/>
-      <c r="D40" s="95" t="s">
+      <c r="D40" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="62"/>
@@ -11965,7 +11972,7 @@
         <v>627</v>
       </c>
       <c r="C41" s="60"/>
-      <c r="D41" s="95" t="s">
+      <c r="D41" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="62"/>
@@ -11983,7 +11990,7 @@
         <v>629</v>
       </c>
       <c r="C42" s="60"/>
-      <c r="D42" s="95" t="s">
+      <c r="D42" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="62"/>
@@ -12015,15 +12022,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12223,10 +12230,10 @@
       <c r="B11" s="19" t="s">
         <v>638</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C11" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23"/>
       <c r="G11" s="24">
@@ -12364,15 +12371,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12464,10 +12471,10 @@
       <c r="B6" s="26" t="s">
         <v>648</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="23"/>
       <c r="G6" s="24">
@@ -12482,10 +12489,10 @@
       <c r="B7" s="19" t="s">
         <v>635</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="22"/>
       <c r="F7" s="23"/>
       <c r="G7" s="24">
@@ -12538,10 +12545,10 @@
       <c r="B10" s="26" t="s">
         <v>649</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="23"/>
       <c r="G10" s="24">
@@ -12591,15 +12598,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12783,10 +12790,10 @@
       <c r="B11" s="19" t="s">
         <v>658</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C11" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23"/>
       <c r="G11" s="24">
@@ -13094,15 +13101,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13172,10 +13179,10 @@
       <c r="B5" s="19" t="s">
         <v>652</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="22"/>
       <c r="F5" s="23"/>
       <c r="G5" s="24">
@@ -13470,10 +13477,10 @@
       <c r="B21" s="19" t="s">
         <v>668</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C21" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="21"/>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
       <c r="G21" s="24">
@@ -13577,15 +13584,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13876,15 +13883,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="96" t="s">
         <v>729</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13952,10 +13959,10 @@
       <c r="B5" s="19" t="s">
         <v>735</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="22"/>
       <c r="F5" s="23"/>
       <c r="G5" s="24">
@@ -13992,10 +13999,10 @@
       <c r="B7" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="22"/>
       <c r="F7" s="23"/>
       <c r="G7" s="24">
@@ -14220,10 +14227,10 @@
       <c r="B19" s="19" t="s">
         <v>763</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C19" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="21"/>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
       <c r="G19" s="24">
@@ -14274,10 +14281,10 @@
       <c r="B22" s="26" t="s">
         <v>769</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C22" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="21"/>
       <c r="E22" s="22"/>
       <c r="F22" s="23"/>
       <c r="G22" s="24">
@@ -14350,10 +14357,10 @@
       <c r="B26" s="26" t="s">
         <v>777</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C26" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="21"/>
       <c r="E26" s="22"/>
       <c r="F26" s="23"/>
       <c r="G26" s="24">
@@ -14534,10 +14541,10 @@
       <c r="B36" s="26" t="s">
         <v>797</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C36" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="21"/>
       <c r="E36" s="22"/>
       <c r="F36" s="23"/>
       <c r="G36" s="24">
@@ -14722,10 +14729,10 @@
       <c r="B46" s="26" t="s">
         <v>817</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C46" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="21"/>
       <c r="E46" s="22"/>
       <c r="F46" s="23"/>
       <c r="G46" s="24">
@@ -14740,10 +14747,10 @@
       <c r="B47" s="19" t="s">
         <v>819</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C47" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="21"/>
       <c r="E47" s="22"/>
       <c r="F47" s="23"/>
       <c r="G47" s="24">
@@ -14758,10 +14765,10 @@
       <c r="B48" s="26" t="s">
         <v>821</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C48" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="21"/>
       <c r="E48" s="22"/>
       <c r="F48" s="23"/>
       <c r="G48" s="24">
@@ -14834,10 +14841,10 @@
       <c r="B52" s="26" t="s">
         <v>829</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C52" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="21"/>
       <c r="E52" s="22"/>
       <c r="F52" s="23"/>
       <c r="G52" s="24">
@@ -14892,10 +14899,10 @@
       <c r="B55" s="19" t="s">
         <v>835</v>
       </c>
-      <c r="C55" s="20"/>
-      <c r="D55" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C55" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="21"/>
       <c r="E55" s="22"/>
       <c r="F55" s="23"/>
       <c r="G55" s="24">
@@ -15012,10 +15019,10 @@
       <c r="B61" s="19" t="s">
         <v>847</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C61" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="21"/>
       <c r="E61" s="22"/>
       <c r="F61" s="23"/>
       <c r="G61" s="24">
@@ -15129,7 +15136,7 @@
       </c>
       <c r="F67" s="23"/>
       <c r="G67" s="24">
-        <f t="shared" ref="G67:G98" si="2">MAX(0,IF(E67="",0,E67)-IF(F67="",0,F67))</f>
+        <f t="shared" ref="G67:G82" si="2">MAX(0,IF(E67="",0,E67)-IF(F67="",0,F67))</f>
         <v>1</v>
       </c>
     </row>
@@ -15415,15 +15422,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15950,15 +15957,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16195,7 +16202,7 @@
         <v>155</v>
       </c>
       <c r="C14" s="60"/>
-      <c r="D14" s="95" t="s">
+      <c r="D14" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="62"/>
@@ -16363,7 +16370,7 @@
         <v>166</v>
       </c>
       <c r="C22" s="60"/>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="62"/>
@@ -16380,10 +16387,10 @@
       <c r="B23" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C23" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="61"/>
       <c r="E23" s="62"/>
       <c r="F23" s="63"/>
       <c r="G23" s="64">
@@ -16413,13 +16420,13 @@
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="95" t="s">
-        <v>10</v>
-      </c>
+      <c r="C25" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="72"/>
       <c r="E25" s="62"/>
       <c r="F25" s="63"/>
       <c r="G25" s="64">
@@ -16467,15 +16474,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16878,7 +16885,7 @@
         <v>189</v>
       </c>
       <c r="C22" s="60"/>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="62"/>
@@ -16946,15 +16953,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="A1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16986,10 +16993,10 @@
       <c r="B3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C3" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="61"/>
       <c r="E3" s="62"/>
       <c r="F3" s="63"/>
       <c r="G3" s="64">
@@ -17041,9 +17048,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="60"/>
-      <c r="D6" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="D6" s="61"/>
       <c r="E6" s="62"/>
       <c r="F6" s="63"/>
       <c r="G6" s="64">
@@ -17058,10 +17063,10 @@
       <c r="B7" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="95" t="s">
-        <v>10</v>
-      </c>
+      <c r="C7" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="72"/>
       <c r="E7" s="62"/>
       <c r="F7" s="63"/>
       <c r="G7" s="64">
@@ -17229,7 +17234,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="60"/>
-      <c r="D16" s="95" t="s">
+      <c r="D16" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="62"/>
@@ -17447,15 +17452,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -17505,10 +17510,10 @@
       <c r="B4" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="61"/>
       <c r="E4" s="62"/>
       <c r="F4" s="63"/>
       <c r="G4" s="64">
@@ -17523,10 +17528,10 @@
       <c r="B5" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="61"/>
       <c r="E5" s="62"/>
       <c r="F5" s="63"/>
       <c r="G5" s="64">
@@ -17563,10 +17568,10 @@
       <c r="B7" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C7" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="61"/>
       <c r="E7" s="62"/>
       <c r="F7" s="63"/>
       <c r="G7" s="64">
@@ -17956,15 +17961,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -18168,10 +18173,10 @@
       <c r="B12" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C12" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="61"/>
       <c r="E12" s="62">
         <v>1</v>
       </c>
@@ -18357,7 +18362,7 @@
         <v>236</v>
       </c>
       <c r="C22" s="60"/>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="72" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="62"/>
@@ -18396,10 +18401,10 @@
       <c r="B24" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="60"/>
-      <c r="D24" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C24" s="97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="61"/>
       <c r="E24" s="62"/>
       <c r="F24" s="63"/>
       <c r="G24" s="64">
@@ -18451,15 +18456,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -18838,14 +18843,14 @@
       </c>
       <c r="D21" s="48"/>
       <c r="E21" s="55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="56">
         <v>2</v>
       </c>
       <c r="G21" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18855,10 +18860,10 @@
       <c r="B22" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="44" t="s">
-        <v>10</v>
-      </c>
+      <c r="C22" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="44"/>
       <c r="E22" s="45"/>
       <c r="F22" s="46"/>
       <c r="G22" s="40">

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1139150A-C44D-4496-A02C-83C3C6D9C179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8E520B-D827-47CC-94E6-7F27CEDD86D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3397,6 +3397,12 @@
     <xf numFmtId="0" fontId="10" fillId="46" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3423,9 +3429,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3462,9 +3465,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3777,15 +3777,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="F10" s="7">
         <f>SUM('ELCHE CF'!F3:F25)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="8">
         <f>SUM('ELCHE CF'!G3:G25)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4419,11 +4419,11 @@
       </c>
       <c r="F24" s="7">
         <f>SUM('LALIGA FANTASY'!F3:F11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="8">
         <f>SUM('LALIGA FANTASY'!G3:G11)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4588,21 +4588,21 @@
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
@@ -4632,15 +4632,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4892,7 +4892,7 @@
       <c r="B14" s="66" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="97" t="s">
+      <c r="C14" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="61"/>
@@ -5145,15 +5145,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5223,7 +5223,7 @@
       <c r="B5" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="61"/>
@@ -5598,15 +5598,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5638,7 +5638,7 @@
       <c r="B3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="61"/>
@@ -5770,7 +5770,7 @@
       <c r="B10" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="61"/>
@@ -5788,7 +5788,7 @@
       <c r="B11" s="59" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="72"/>
@@ -6090,7 +6090,7 @@
       <c r="B26" s="66" t="s">
         <v>332</v>
       </c>
-      <c r="C26" s="97" t="s">
+      <c r="C26" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="61"/>
@@ -6123,15 +6123,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6429,7 +6429,7 @@
       <c r="B16" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="61"/>
@@ -6473,7 +6473,7 @@
       <c r="B18" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="61"/>
@@ -6698,15 +6698,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6874,7 +6874,7 @@
       <c r="B10" s="66" t="s">
         <v>371</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="61"/>
@@ -6994,7 +6994,7 @@
       <c r="B16" s="66" t="s">
         <v>377</v>
       </c>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="61"/>
@@ -7058,7 +7058,7 @@
       <c r="B19" s="59" t="s">
         <v>380</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="61"/>
@@ -7193,15 +7193,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -7469,7 +7469,7 @@
       <c r="B15" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="61"/>
@@ -7694,15 +7694,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -7916,7 +7916,7 @@
       <c r="B13" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="61"/>
@@ -8235,15 +8235,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -8575,7 +8575,7 @@
       <c r="B18" s="66" t="s">
         <v>448</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="61"/>
@@ -8629,7 +8629,7 @@
       <c r="B21" s="59" t="s">
         <v>451</v>
       </c>
-      <c r="C21" s="97" t="s">
+      <c r="C21" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="61"/>
@@ -8647,7 +8647,7 @@
       <c r="B22" s="66" t="s">
         <v>452</v>
       </c>
-      <c r="C22" s="97" t="s">
+      <c r="C22" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="61"/>
@@ -8738,15 +8738,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9189,15 +9189,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9251,7 +9251,7 @@
       <c r="B4" s="66" t="s">
         <v>476</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="61"/>
@@ -9343,7 +9343,7 @@
       <c r="B9" s="59" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="72"/>
@@ -9519,7 +9519,7 @@
       <c r="B18" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="61"/>
@@ -9561,7 +9561,7 @@
       <c r="B20" s="66" t="s">
         <v>492</v>
       </c>
-      <c r="C20" s="97" t="s">
+      <c r="C20" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="61"/>
@@ -9716,15 +9716,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9872,7 +9872,7 @@
       <c r="B9" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="61"/>
@@ -9960,7 +9960,7 @@
       <c r="B14" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="97" t="s">
+      <c r="C14" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="61"/>
@@ -10004,7 +10004,7 @@
       <c r="B16" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="61"/>
@@ -10144,7 +10144,7 @@
       <c r="B23" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="61"/>
@@ -10219,15 +10219,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -10736,15 +10736,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -11247,15 +11247,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="91" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
@@ -11287,7 +11287,7 @@
       <c r="B3" s="59" t="s">
         <v>551</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="61"/>
@@ -11539,7 +11539,7 @@
       <c r="B17" s="59" t="s">
         <v>579</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="61"/>
@@ -12022,15 +12022,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12371,15 +12371,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12570,10 +12570,12 @@
       <c r="E11" s="22">
         <v>1</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="23">
+        <v>1</v>
+      </c>
       <c r="G11" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12598,15 +12600,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13101,15 +13103,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13584,15 +13586,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13883,15 +13885,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="97" t="s">
         <v>729</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15422,15 +15424,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15957,15 +15959,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16387,7 +16389,7 @@
       <c r="B23" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="61"/>
@@ -16423,7 +16425,7 @@
       <c r="B25" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="C25" s="97" t="s">
+      <c r="C25" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="72"/>
@@ -16474,15 +16476,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16953,15 +16955,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16993,7 +16995,7 @@
       <c r="B3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="61"/>
@@ -17063,7 +17065,7 @@
       <c r="B7" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="72"/>
@@ -17452,15 +17454,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -17510,7 +17512,7 @@
       <c r="B4" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="61"/>
@@ -17528,7 +17530,7 @@
       <c r="B5" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="61"/>
@@ -17568,7 +17570,7 @@
       <c r="B7" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="61"/>
@@ -17961,15 +17963,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -18173,7 +18175,7 @@
       <c r="B12" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="61"/>
@@ -18401,7 +18403,7 @@
       <c r="B24" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="97" t="s">
+      <c r="C24" s="74" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="61"/>
@@ -18456,15 +18458,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -18846,11 +18848,11 @@
         <v>4</v>
       </c>
       <c r="F21" s="56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8E520B-D827-47CC-94E6-7F27CEDD86D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F9AD8C-622B-44C4-8163-FA1AB78FF898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3431,6 +3431,9 @@
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3450,9 +3453,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3770,13 +3770,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="77" t="s">
         <v>55</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>60</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>63</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>65</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>67</v>
       </c>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="F12" s="7">
         <f>SUM('GETAFE CF'!F3:F23)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="8">
         <f>SUM('GETAFE CF'!G3:G23)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>68</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>69</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>71</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>73</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>74</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>77</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>78</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>79</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>81</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>83</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>84</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>85</v>
       </c>
@@ -4588,14 +4588,14 @@
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="76"/>
       <c r="B31" s="76"/>
       <c r="C31" s="76"/>
@@ -4604,7 +4604,7 @@
       <c r="F31" s="76"/>
       <c r="G31" s="76"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
         <v>86</v>
       </c>
@@ -4621,7 +4621,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4631,7 +4631,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
         <v>66</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>275</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>283</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -5134,7 +5134,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5144,7 +5144,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="85" t="s">
         <v>67</v>
       </c>
@@ -5155,7 +5155,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>29</v>
       </c>
@@ -5346,13 +5346,15 @@
       <c r="E11" s="62">
         <v>1</v>
       </c>
-      <c r="F11" s="63"/>
+      <c r="F11" s="63">
+        <v>1</v>
+      </c>
       <c r="G11" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
@@ -5370,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>33</v>
       </c>
@@ -5392,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>37</v>
       </c>
@@ -5410,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>39</v>
       </c>
@@ -5428,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>41</v>
       </c>
@@ -5446,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>43</v>
       </c>
@@ -5464,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>45</v>
       </c>
@@ -5482,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>47</v>
       </c>
@@ -5502,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>49</v>
       </c>
@@ -5520,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>51</v>
       </c>
@@ -5540,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>214</v>
       </c>
@@ -5558,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>53</v>
       </c>
@@ -5587,7 +5589,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5597,8 +5599,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="86" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="76"/>
@@ -5608,7 +5610,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5631,7 +5633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5649,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5667,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5685,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5703,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5725,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5745,7 +5747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -5763,7 +5765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -5781,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -5803,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -5825,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -5845,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -5867,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -5889,7 +5891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -5911,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>159</v>
       </c>
@@ -5931,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>161</v>
       </c>
@@ -5949,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5967,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -5987,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -6005,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -6027,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -6045,7 +6047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -6067,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -6083,7 +6085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>111</v>
       </c>
@@ -6112,7 +6114,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6122,8 +6124,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="76"/>
@@ -6133,7 +6135,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6156,7 +6158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6178,7 +6180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6196,7 +6198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6218,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6236,7 +6238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6258,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6280,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -6302,7 +6304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -6322,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6344,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6362,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>343</v>
       </c>
@@ -6384,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>345</v>
       </c>
@@ -6404,7 +6406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -6422,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -6444,7 +6446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -6466,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -6488,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>351</v>
       </c>
@@ -6510,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>353</v>
       </c>
@@ -6530,7 +6532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>355</v>
       </c>
@@ -6550,7 +6552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>357</v>
       </c>
@@ -6572,7 +6574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -6592,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>360</v>
       </c>
@@ -6610,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -6632,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -6654,7 +6656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -6687,7 +6689,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6697,7 +6699,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
         <v>70</v>
       </c>
@@ -6708,7 +6710,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6731,7 +6733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6749,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6767,7 +6769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6785,7 +6787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6807,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6829,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6851,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -6867,7 +6869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -6889,7 +6891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6911,7 +6913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6933,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -6951,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -6969,7 +6971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -6987,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7009,7 +7011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7029,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7051,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7069,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7087,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -7109,7 +7111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>49</v>
       </c>
@@ -7131,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -7153,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -7182,7 +7184,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7192,7 +7194,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
         <v>71</v>
       </c>
@@ -7203,7 +7205,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7226,7 +7228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7248,7 +7250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7270,7 +7272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7288,7 +7290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7306,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>19</v>
       </c>
@@ -7324,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>21</v>
       </c>
@@ -7344,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>23</v>
       </c>
@@ -7362,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7380,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7402,7 +7404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -7422,7 +7424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -7440,7 +7442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -7462,7 +7464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -7480,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7502,7 +7504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7518,7 +7520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7536,7 +7538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7554,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7574,7 +7576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -7592,7 +7594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -7610,7 +7612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -7632,7 +7634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -7654,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -7683,7 +7685,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7693,7 +7695,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="84" t="s">
         <v>72</v>
       </c>
@@ -7704,7 +7706,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7727,7 +7729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7745,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7763,7 +7765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7781,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7801,7 +7803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -7819,7 +7821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -7835,7 +7837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -7853,7 +7855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7875,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7891,7 +7893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -7909,7 +7911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -7931,7 +7933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -7953,7 +7955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -7975,7 +7977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -7997,7 +7999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8015,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8037,7 +8039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>131</v>
       </c>
@@ -8057,7 +8059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>41</v>
       </c>
@@ -8077,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>43</v>
       </c>
@@ -8097,7 +8099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>283</v>
       </c>
@@ -8115,7 +8117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>45</v>
       </c>
@@ -8133,7 +8135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>47</v>
       </c>
@@ -8155,7 +8157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -8173,7 +8175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -8191,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -8224,7 +8226,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8234,8 +8236,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>73</v>
       </c>
       <c r="B1" s="76"/>
@@ -8245,7 +8247,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8268,7 +8270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -8290,7 +8292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -8308,7 +8310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -8330,7 +8332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -8348,7 +8350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -8370,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -8388,7 +8390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -8408,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -8430,7 +8432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -8452,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -8470,7 +8472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -8490,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -8508,7 +8510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>443</v>
       </c>
@@ -8530,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>445</v>
       </c>
@@ -8546,7 +8548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8568,7 +8570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8586,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -8604,7 +8606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -8622,7 +8624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -8640,7 +8642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -8658,7 +8660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -8678,7 +8680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -8696,7 +8698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -8727,7 +8729,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8737,7 +8739,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
         <v>74</v>
       </c>
@@ -8748,7 +8750,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8771,7 +8773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -8789,7 +8791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -8807,7 +8809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -8825,7 +8827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -8847,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -8869,7 +8871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -8887,7 +8889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -8905,7 +8907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>27</v>
       </c>
@@ -8923,7 +8925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -8941,7 +8943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>31</v>
       </c>
@@ -8959,7 +8961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>33</v>
       </c>
@@ -8977,7 +8979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>37</v>
       </c>
@@ -8995,7 +8997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>254</v>
       </c>
@@ -9017,7 +9019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
         <v>256</v>
       </c>
@@ -9033,7 +9035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -9051,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -9073,7 +9075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -9095,7 +9097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -9113,7 +9115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>49</v>
       </c>
@@ -9131,7 +9133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>51</v>
       </c>
@@ -9149,7 +9151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>53</v>
       </c>
@@ -9178,7 +9180,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9188,8 +9190,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="89" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="76"/>
@@ -9199,7 +9201,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9222,7 +9224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9244,7 +9246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9262,7 +9264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9280,7 +9282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9298,7 +9300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9316,7 +9318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9336,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -9354,7 +9356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -9376,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -9392,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -9410,7 +9412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -9430,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -9452,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -9470,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -9490,7 +9492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -9512,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -9534,7 +9536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -9554,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -9572,7 +9574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -9590,7 +9592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -9612,7 +9614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -9634,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -9654,7 +9656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -9672,7 +9674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -9705,7 +9707,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9715,7 +9717,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>59</v>
       </c>
@@ -9726,7 +9728,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9749,7 +9751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9771,7 +9773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9789,7 +9791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9811,7 +9813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9829,7 +9831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9847,7 +9849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9865,7 +9867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -9883,7 +9885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -9899,7 +9901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -9917,7 +9919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -9935,7 +9937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -9953,7 +9955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -9975,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -9997,7 +9999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -10015,7 +10017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -10033,7 +10035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -10055,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -10077,7 +10079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -10099,7 +10101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>106</v>
       </c>
@@ -10119,7 +10121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>107</v>
       </c>
@@ -10137,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -10159,7 +10161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -10181,7 +10183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>111</v>
       </c>
@@ -10208,7 +10210,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10218,8 +10220,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="90" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="76"/>
@@ -10229,7 +10231,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10252,7 +10254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10270,7 +10272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10288,7 +10290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10306,7 +10308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10328,7 +10330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -10350,7 +10352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -10372,7 +10374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -10390,7 +10392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>149</v>
       </c>
@@ -10410,7 +10412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>95</v>
       </c>
@@ -10428,7 +10430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>29</v>
       </c>
@@ -10450,7 +10452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>31</v>
       </c>
@@ -10468,7 +10470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>33</v>
       </c>
@@ -10486,7 +10488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>37</v>
       </c>
@@ -10504,7 +10506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>39</v>
       </c>
@@ -10522,7 +10524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -10544,7 +10546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -10562,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -10584,7 +10586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
         <v>165</v>
       </c>
@@ -10602,7 +10604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>47</v>
       </c>
@@ -10620,7 +10622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>49</v>
       </c>
@@ -10638,7 +10640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>51</v>
       </c>
@@ -10654,7 +10656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="52" t="s">
         <v>214</v>
       </c>
@@ -10672,7 +10674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>520</v>
       </c>
@@ -10694,7 +10696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>522</v>
       </c>
@@ -10725,7 +10727,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10735,8 +10737,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="91" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="76"/>
@@ -10746,7 +10748,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10769,7 +10771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10791,7 +10793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10811,7 +10813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10833,7 +10835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10849,7 +10851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>17</v>
       </c>
@@ -10867,7 +10869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -10889,7 +10891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>117</v>
       </c>
@@ -10909,7 +10911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>119</v>
       </c>
@@ -10927,7 +10929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>531</v>
       </c>
@@ -10945,7 +10947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>533</v>
       </c>
@@ -10963,7 +10965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>149</v>
       </c>
@@ -10983,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>95</v>
       </c>
@@ -10999,7 +11001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>29</v>
       </c>
@@ -11017,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>31</v>
       </c>
@@ -11035,7 +11037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>33</v>
       </c>
@@ -11053,7 +11055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>37</v>
       </c>
@@ -11071,7 +11073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>39</v>
       </c>
@@ -11093,7 +11095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>41</v>
       </c>
@@ -11111,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>43</v>
       </c>
@@ -11129,7 +11131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>45</v>
       </c>
@@ -11151,7 +11153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>47</v>
       </c>
@@ -11169,7 +11171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -11187,7 +11189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -11205,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -11236,7 +11238,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -11246,8 +11248,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="92" t="s">
         <v>549</v>
       </c>
       <c r="B1" s="76"/>
@@ -11257,7 +11259,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
@@ -11280,7 +11282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>550</v>
       </c>
@@ -11298,7 +11300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>552</v>
       </c>
@@ -11316,7 +11318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>554</v>
       </c>
@@ -11334,7 +11336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>556</v>
       </c>
@@ -11352,7 +11354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>558</v>
       </c>
@@ -11370,7 +11372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>560</v>
       </c>
@@ -11388,7 +11390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>562</v>
       </c>
@@ -11406,7 +11408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>564</v>
       </c>
@@ -11424,7 +11426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>566</v>
       </c>
@@ -11442,7 +11444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>568</v>
       </c>
@@ -11460,7 +11462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>570</v>
       </c>
@@ -11478,7 +11480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>572</v>
       </c>
@@ -11496,7 +11498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>574</v>
       </c>
@@ -11514,7 +11516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>576</v>
       </c>
@@ -11532,7 +11534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>578</v>
       </c>
@@ -11550,7 +11552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>580</v>
       </c>
@@ -11568,7 +11570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>582</v>
       </c>
@@ -11586,7 +11588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>584</v>
       </c>
@@ -11604,7 +11606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>586</v>
       </c>
@@ -11622,7 +11624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>588</v>
       </c>
@@ -11640,7 +11642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>590</v>
       </c>
@@ -11658,7 +11660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>592</v>
       </c>
@@ -11676,7 +11678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>594</v>
       </c>
@@ -11694,7 +11696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>596</v>
       </c>
@@ -11712,7 +11714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>598</v>
       </c>
@@ -11730,7 +11732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="65" t="s">
         <v>600</v>
       </c>
@@ -11748,7 +11750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58" t="s">
         <v>602</v>
       </c>
@@ -11766,7 +11768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
         <v>604</v>
       </c>
@@ -11784,7 +11786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58" t="s">
         <v>606</v>
       </c>
@@ -11802,7 +11804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65" t="s">
         <v>608</v>
       </c>
@@ -11820,7 +11822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58" t="s">
         <v>610</v>
       </c>
@@ -11838,7 +11840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="65" t="s">
         <v>612</v>
       </c>
@@ -11856,7 +11858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58" t="s">
         <v>614</v>
       </c>
@@ -11874,7 +11876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="65" t="s">
         <v>616</v>
       </c>
@@ -11892,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
         <v>618</v>
       </c>
@@ -11910,7 +11912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="65" t="s">
         <v>620</v>
       </c>
@@ -11928,7 +11930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58" t="s">
         <v>622</v>
       </c>
@@ -11946,7 +11948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65" t="s">
         <v>624</v>
       </c>
@@ -11964,7 +11966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
         <v>626</v>
       </c>
@@ -11982,7 +11984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="65" t="s">
         <v>628</v>
       </c>
@@ -12011,7 +12013,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12021,8 +12023,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="93" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="76"/>
@@ -12032,7 +12034,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12055,7 +12057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12073,7 +12075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12095,7 +12097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12117,7 +12119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12139,7 +12141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12161,7 +12163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12183,7 +12185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12205,7 +12207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12223,7 +12225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12241,7 +12243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12259,7 +12261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12277,7 +12279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12295,7 +12297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12313,7 +12315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12331,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12360,7 +12362,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12370,8 +12372,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="76"/>
@@ -12381,7 +12383,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12404,7 +12406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12422,7 +12424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12444,7 +12446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12464,7 +12466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12482,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12500,7 +12502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12518,7 +12520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12538,7 +12540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12556,7 +12558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12589,7 +12591,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12599,7 +12601,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="94" t="s">
         <v>80</v>
       </c>
@@ -12610,7 +12612,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12633,7 +12635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12655,7 +12657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12673,7 +12675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12691,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12713,7 +12715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12731,7 +12733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12749,7 +12751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12767,7 +12769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12785,7 +12787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12803,7 +12805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12821,7 +12823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12839,7 +12841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12857,7 +12859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12879,7 +12881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12899,7 +12901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12917,7 +12919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>45</v>
       </c>
@@ -12935,7 +12937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>47</v>
       </c>
@@ -12957,7 +12959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>49</v>
       </c>
@@ -12979,7 +12981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>51</v>
       </c>
@@ -12997,7 +12999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>53</v>
       </c>
@@ -13019,7 +13021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>670</v>
       </c>
@@ -13037,7 +13039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>672</v>
       </c>
@@ -13059,7 +13061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>674</v>
       </c>
@@ -13092,7 +13094,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13102,7 +13104,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>81</v>
       </c>
@@ -13113,7 +13115,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13136,7 +13138,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>676</v>
       </c>
@@ -13154,7 +13156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>677</v>
       </c>
@@ -13174,7 +13176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>678</v>
       </c>
@@ -13192,7 +13194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>679</v>
       </c>
@@ -13210,7 +13212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>680</v>
       </c>
@@ -13232,7 +13234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>681</v>
       </c>
@@ -13250,7 +13252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>682</v>
       </c>
@@ -13268,7 +13270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>683</v>
       </c>
@@ -13286,7 +13288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>684</v>
       </c>
@@ -13304,7 +13306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>685</v>
       </c>
@@ -13322,7 +13324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>686</v>
       </c>
@@ -13340,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>687</v>
       </c>
@@ -13360,7 +13362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>688</v>
       </c>
@@ -13378,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>689</v>
       </c>
@@ -13396,7 +13398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>690</v>
       </c>
@@ -13414,7 +13416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>691</v>
       </c>
@@ -13432,7 +13434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>692</v>
       </c>
@@ -13454,7 +13456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>693</v>
       </c>
@@ -13472,7 +13474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>694</v>
       </c>
@@ -13490,7 +13492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>695</v>
       </c>
@@ -13508,7 +13510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>696</v>
       </c>
@@ -13528,7 +13530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>697</v>
       </c>
@@ -13546,7 +13548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>698</v>
       </c>
@@ -13575,7 +13577,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13585,7 +13587,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="96" t="s">
         <v>82</v>
       </c>
@@ -13596,7 +13598,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13619,7 +13621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>699</v>
       </c>
@@ -13635,7 +13637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>701</v>
       </c>
@@ -13651,7 +13653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>703</v>
       </c>
@@ -13667,7 +13669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>705</v>
       </c>
@@ -13683,7 +13685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>707</v>
       </c>
@@ -13699,7 +13701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>709</v>
       </c>
@@ -13715,7 +13717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>711</v>
       </c>
@@ -13731,7 +13733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>713</v>
       </c>
@@ -13747,7 +13749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>715</v>
       </c>
@@ -13765,7 +13767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>717</v>
       </c>
@@ -13781,7 +13783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>719</v>
       </c>
@@ -13797,7 +13799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>721</v>
       </c>
@@ -13813,7 +13815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>723</v>
       </c>
@@ -13831,7 +13833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>725</v>
       </c>
@@ -13847,7 +13849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>727</v>
       </c>
@@ -13874,7 +13876,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13884,7 +13886,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="97" t="s">
         <v>729</v>
       </c>
@@ -13895,7 +13897,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13918,7 +13920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>730</v>
       </c>
@@ -13936,7 +13938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>732</v>
       </c>
@@ -13954,7 +13956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>734</v>
       </c>
@@ -13972,7 +13974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>736</v>
       </c>
@@ -13994,7 +13996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>738</v>
       </c>
@@ -14012,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>740</v>
       </c>
@@ -14030,7 +14032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>742</v>
       </c>
@@ -14048,7 +14050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>744</v>
       </c>
@@ -14066,7 +14068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>746</v>
       </c>
@@ -14088,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>748</v>
       </c>
@@ -14110,7 +14112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>750</v>
       </c>
@@ -14128,7 +14130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>752</v>
       </c>
@@ -14146,7 +14148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>754</v>
       </c>
@@ -14164,7 +14166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>756</v>
       </c>
@@ -14182,7 +14184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>758</v>
       </c>
@@ -14200,7 +14202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>760</v>
       </c>
@@ -14222,7 +14224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>762</v>
       </c>
@@ -14240,7 +14242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>764</v>
       </c>
@@ -14258,7 +14260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>766</v>
       </c>
@@ -14276,7 +14278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>768</v>
       </c>
@@ -14294,7 +14296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>770</v>
       </c>
@@ -14316,7 +14318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>772</v>
       </c>
@@ -14334,7 +14336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>774</v>
       </c>
@@ -14352,7 +14354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>776</v>
       </c>
@@ -14370,7 +14372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>778</v>
       </c>
@@ -14388,7 +14390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>780</v>
       </c>
@@ -14406,7 +14408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>782</v>
       </c>
@@ -14424,7 +14426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>784</v>
       </c>
@@ -14446,7 +14448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>786</v>
       </c>
@@ -14464,7 +14466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>788</v>
       </c>
@@ -14482,7 +14484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>790</v>
       </c>
@@ -14500,7 +14502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
         <v>792</v>
       </c>
@@ -14518,7 +14520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>794</v>
       </c>
@@ -14536,7 +14538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>796</v>
       </c>
@@ -14554,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>798</v>
       </c>
@@ -14576,7 +14578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>800</v>
       </c>
@@ -14598,7 +14600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
         <v>802</v>
       </c>
@@ -14616,7 +14618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>804</v>
       </c>
@@ -14634,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>806</v>
       </c>
@@ -14652,7 +14654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
         <v>808</v>
       </c>
@@ -14670,7 +14672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>810</v>
       </c>
@@ -14688,7 +14690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
         <v>812</v>
       </c>
@@ -14706,7 +14708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>814</v>
       </c>
@@ -14724,7 +14726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="25" t="s">
         <v>816</v>
       </c>
@@ -14742,7 +14744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>818</v>
       </c>
@@ -14760,7 +14762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="25" t="s">
         <v>820</v>
       </c>
@@ -14778,7 +14780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>822</v>
       </c>
@@ -14796,7 +14798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="25" t="s">
         <v>824</v>
       </c>
@@ -14818,7 +14820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
         <v>826</v>
       </c>
@@ -14836,7 +14838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="25" t="s">
         <v>828</v>
       </c>
@@ -14854,7 +14856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>830</v>
       </c>
@@ -14876,7 +14878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="25" t="s">
         <v>832</v>
       </c>
@@ -14894,7 +14896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>834</v>
       </c>
@@ -14912,7 +14914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
         <v>836</v>
       </c>
@@ -14934,7 +14936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>838</v>
       </c>
@@ -14956,7 +14958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="25" t="s">
         <v>840</v>
       </c>
@@ -14974,7 +14976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
         <v>842</v>
       </c>
@@ -14996,7 +14998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="25" t="s">
         <v>844</v>
       </c>
@@ -15014,7 +15016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
         <v>846</v>
       </c>
@@ -15032,7 +15034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
         <v>848</v>
       </c>
@@ -15054,7 +15056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>850</v>
       </c>
@@ -15070,7 +15072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
         <v>852</v>
       </c>
@@ -15088,7 +15090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>854</v>
       </c>
@@ -15104,7 +15106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
         <v>856</v>
       </c>
@@ -15124,7 +15126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>858</v>
       </c>
@@ -15142,7 +15144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
         <v>860</v>
       </c>
@@ -15158,7 +15160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
         <v>862</v>
       </c>
@@ -15176,7 +15178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
         <v>864</v>
       </c>
@@ -15192,7 +15194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
         <v>866</v>
       </c>
@@ -15208,7 +15210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
         <v>868</v>
       </c>
@@ -15228,7 +15230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
         <v>870</v>
       </c>
@@ -15244,7 +15246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
         <v>872</v>
       </c>
@@ -15264,7 +15266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
         <v>874</v>
       </c>
@@ -15280,7 +15282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
         <v>876</v>
       </c>
@@ -15296,7 +15298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
         <v>878</v>
       </c>
@@ -15312,7 +15314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="25" t="s">
         <v>880</v>
       </c>
@@ -15328,7 +15330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
         <v>882</v>
       </c>
@@ -15346,7 +15348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="25" t="s">
         <v>884</v>
       </c>
@@ -15362,7 +15364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
         <v>886</v>
       </c>
@@ -15382,7 +15384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="25" t="s">
         <v>888</v>
       </c>
@@ -15413,7 +15415,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15423,7 +15425,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
         <v>60</v>
       </c>
@@ -15434,7 +15436,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15457,7 +15459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -15475,7 +15477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -15495,7 +15497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -15513,7 +15515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -15535,7 +15537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -15553,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>117</v>
       </c>
@@ -15569,7 +15571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>119</v>
       </c>
@@ -15591,7 +15593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -15613,7 +15615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -15635,7 +15637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -15653,7 +15655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -15669,7 +15671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -15691,7 +15693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -15713,7 +15715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -15735,7 +15737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>39</v>
       </c>
@@ -15751,7 +15753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>131</v>
       </c>
@@ -15769,7 +15771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -15787,7 +15789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -15809,7 +15811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -15831,7 +15833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>136</v>
       </c>
@@ -15851,7 +15853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>138</v>
       </c>
@@ -15873,7 +15875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -15895,7 +15897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -15917,7 +15919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -15948,7 +15950,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15958,7 +15960,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
         <v>61</v>
       </c>
@@ -15969,7 +15971,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15992,7 +15994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16010,7 +16012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16028,7 +16030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16046,7 +16048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16064,7 +16066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16082,7 +16084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -16098,7 +16100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -16120,7 +16122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>149</v>
       </c>
@@ -16138,7 +16140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -16158,7 +16160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16176,7 +16178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16196,7 +16198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -16214,7 +16216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -16236,7 +16238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -16258,7 +16260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -16280,7 +16282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>159</v>
       </c>
@@ -16302,7 +16304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>161</v>
       </c>
@@ -16322,7 +16324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -16344,7 +16346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -16364,7 +16366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>165</v>
       </c>
@@ -16382,7 +16384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -16400,7 +16402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>49</v>
       </c>
@@ -16418,7 +16420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
@@ -16436,7 +16438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -16465,7 +16467,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16475,7 +16477,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
         <v>62</v>
       </c>
@@ -16486,7 +16488,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16509,7 +16511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16527,7 +16529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16549,7 +16551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16567,7 +16569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16589,7 +16591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16607,7 +16609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>117</v>
       </c>
@@ -16627,7 +16629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>119</v>
       </c>
@@ -16645,7 +16647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -16663,7 +16665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -16681,7 +16683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16703,7 +16705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16725,7 +16727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -16747,7 +16749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -16769,7 +16771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -16787,7 +16789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -16805,7 +16807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -16823,7 +16825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -16841,7 +16843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -16859,7 +16861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>49</v>
       </c>
@@ -16879,7 +16881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>188</v>
       </c>
@@ -16897,7 +16899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -16915,7 +16917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -16944,7 +16946,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16954,7 +16956,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
@@ -16965,7 +16967,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16988,7 +16990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17006,7 +17008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17024,7 +17026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17042,7 +17044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17058,7 +17060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>17</v>
       </c>
@@ -17076,7 +17078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>19</v>
       </c>
@@ -17092,7 +17094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>21</v>
       </c>
@@ -17114,7 +17116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>23</v>
       </c>
@@ -17132,7 +17134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>25</v>
       </c>
@@ -17150,7 +17152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>27</v>
       </c>
@@ -17172,7 +17174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>29</v>
       </c>
@@ -17190,7 +17192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -17208,7 +17210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -17228,7 +17230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
@@ -17246,7 +17248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -17264,7 +17266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -17286,7 +17288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -17308,7 +17310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -17330,7 +17332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -17352,7 +17354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -17374,7 +17376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -17396,7 +17398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17414,7 +17416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -17443,7 +17445,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17453,7 +17455,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="82" t="s">
         <v>63</v>
       </c>
@@ -17464,7 +17466,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17487,7 +17489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17505,7 +17507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17523,7 +17525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17541,7 +17543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17563,7 +17565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -17581,7 +17583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -17599,7 +17601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -17621,7 +17623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -17639,7 +17641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>123</v>
       </c>
@@ -17657,7 +17659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>125</v>
       </c>
@@ -17677,7 +17679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -17695,7 +17697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -17713,7 +17715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -17735,7 +17737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -17757,7 +17759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -17779,7 +17781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>206</v>
       </c>
@@ -17795,7 +17797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -17811,7 +17813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -17829,7 +17831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -17847,7 +17849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>106</v>
       </c>
@@ -17869,7 +17871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>107</v>
       </c>
@@ -17885,7 +17887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17907,7 +17909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -17923,7 +17925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -17952,7 +17954,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17962,7 +17964,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
         <v>64</v>
       </c>
@@ -17973,7 +17975,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17996,7 +17998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -18018,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -18036,7 +18038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -18054,7 +18056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -18072,7 +18074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -18090,7 +18092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -18108,7 +18110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -18130,7 +18132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -18152,7 +18154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>224</v>
       </c>
@@ -18168,7 +18170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>123</v>
       </c>
@@ -18190,7 +18192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>125</v>
       </c>
@@ -18210,7 +18212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -18228,7 +18230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -18246,7 +18248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -18264,7 +18266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -18282,7 +18284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -18300,7 +18302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>206</v>
       </c>
@@ -18316,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -18334,7 +18336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -18356,7 +18358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -18374,7 +18376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -18396,7 +18398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -18414,7 +18416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -18447,7 +18449,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -18457,7 +18459,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="84" t="s">
         <v>65</v>
       </c>
@@ -18468,7 +18470,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18491,7 +18493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -18509,7 +18511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
         <v>11</v>
       </c>
@@ -18525,7 +18527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>241</v>
       </c>
@@ -18543,7 +18545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -18565,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>15</v>
       </c>
@@ -18583,7 +18585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -18599,7 +18601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>23</v>
       </c>
@@ -18617,7 +18619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -18635,7 +18637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -18651,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -18671,7 +18673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -18689,7 +18691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -18711,7 +18713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -18733,7 +18735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -18751,7 +18753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
@@ -18773,7 +18775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>256</v>
       </c>
@@ -18789,7 +18791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -18811,7 +18813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -18833,7 +18835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -18855,7 +18857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -18873,7 +18875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>49</v>
       </c>
@@ -18891,7 +18893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>51</v>
       </c>
@@ -18913,7 +18915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>53</v>
       </c>

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F9AD8C-622B-44C4-8163-FA1AB78FF898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FD8E0D-921B-413B-8016-E99634A8B675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3428,9 +3428,6 @@
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3453,6 +3450,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3770,13 +3770,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>55</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -3831,14 +3831,14 @@
       </c>
       <c r="F3" s="7">
         <f>SUM('D. ALAVÉS'!F3:F25)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8">
         <f>SUM('D. ALAVÉS'!G3:G25)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>60</v>
       </c>
@@ -3859,14 +3859,14 @@
       </c>
       <c r="F4" s="7">
         <f>SUM('ATHLETIC CLUB'!F3:F26)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="8">
         <f>SUM('ATHLETIC CLUB'!G3:G26)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -3939,18 +3939,18 @@
       </c>
       <c r="E7" s="6">
         <f>SUMIF('REAL BETIS'!E3:E25,"&gt;"&amp;0,'REAL BETIS'!E3:E25)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" s="7">
         <f>SUM('REAL BETIS'!F3:F25)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="8">
         <f>SUM('REAL BETIS'!G3:G25)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>63</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>65</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -4055,14 +4055,14 @@
       </c>
       <c r="F11" s="7">
         <f>SUM('RCD ESPANYOL'!F3:F25)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" s="8">
         <f>SUM('RCD ESPANYOL'!G3:G25)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>67</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>68</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>69</v>
       </c>
@@ -4139,14 +4139,14 @@
       </c>
       <c r="F14" s="7">
         <f>SUM('REAL MADRID CF'!F3:F27)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="8">
         <f>SUM('REAL MADRID CF'!G3:G27)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
@@ -4167,14 +4167,14 @@
       </c>
       <c r="F15" s="7">
         <f>SUM('MÁLAGA CF'!F3:F24)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G15" s="8">
         <f>SUM('MÁLAGA CF'!G3:G24)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>71</v>
       </c>
@@ -4195,14 +4195,14 @@
       </c>
       <c r="F16" s="7">
         <f>SUM('CA OSASUNA'!F3:F25)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="8">
         <f>SUM('CA OSASUNA'!G3:G25)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>73</v>
       </c>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="F18" s="7">
         <f>SUM('RAYO VALLECANO'!F3:F25)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="8">
         <f>SUM('RAYO VALLECANO'!G3:G25)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>74</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>77</v>
       </c>
@@ -4363,14 +4363,14 @@
       </c>
       <c r="F22" s="7">
         <f>SUM('VILLARREAL CF'!F3:F26)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G22" s="8">
         <f>SUM('VILLARREAL CF'!G3:G26)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>78</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>79</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>81</v>
       </c>
@@ -4475,14 +4475,14 @@
       </c>
       <c r="F26" s="7">
         <f>SUM('DRAFT 23 KROMIX'!F3:F25)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G26" s="8">
         <f>SUM('DRAFT 23 KROMIX'!G3:G25)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>83</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
         <v>84</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>85</v>
       </c>
@@ -4584,18 +4584,18 @@
       </c>
       <c r="E30" s="15">
         <f t="shared" si="0"/>
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="76"/>
       <c r="B31" s="76"/>
       <c r="C31" s="76"/>
@@ -4604,7 +4604,7 @@
       <c r="F31" s="76"/>
       <c r="G31" s="76"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>86</v>
       </c>
@@ -4621,7 +4621,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4631,7 +4631,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>66</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>275</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>283</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -5040,14 +5040,14 @@
         <v>2</v>
       </c>
       <c r="F21" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -5134,7 +5134,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5144,8 +5144,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="75" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="76"/>
@@ -5155,7 +5155,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>29</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>33</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>37</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>39</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>41</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>43</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>45</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>47</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>49</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>51</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>214</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>53</v>
       </c>
@@ -5589,7 +5589,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5599,8 +5599,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="85" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="76"/>
@@ -5610,7 +5610,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>159</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>161</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>111</v>
       </c>
@@ -6114,7 +6114,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6124,8 +6124,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="86" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="76"/>
@@ -6135,7 +6135,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>343</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>345</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>351</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>353</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>355</v>
       </c>
@@ -6545,14 +6545,14 @@
         <v>2</v>
       </c>
       <c r="F21" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>357</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>360</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -6689,7 +6689,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6699,7 +6699,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>70</v>
       </c>
@@ -6710,7 +6710,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -6884,14 +6884,14 @@
         <v>3</v>
       </c>
       <c r="F10" s="63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -7104,14 +7104,14 @@
         <v>2</v>
       </c>
       <c r="F21" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>49</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -7184,7 +7184,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7194,7 +7194,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>71</v>
       </c>
@@ -7205,7 +7205,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7243,14 +7243,14 @@
         <v>2</v>
       </c>
       <c r="F3" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="64">
         <f t="shared" ref="G3:G25" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>19</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>21</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>23</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -7418,13 +7418,15 @@
       <c r="E12" s="62">
         <v>1</v>
       </c>
-      <c r="F12" s="63"/>
+      <c r="F12" s="63">
+        <v>1</v>
+      </c>
       <c r="G12" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -7442,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -7464,7 +7466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -7482,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7504,7 +7506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7520,7 +7522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7538,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7556,7 +7558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7576,7 +7578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -7594,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -7612,7 +7614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -7634,7 +7636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -7656,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -7685,7 +7687,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7695,7 +7697,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="84" t="s">
         <v>72</v>
       </c>
@@ -7706,7 +7708,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7729,7 +7731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7747,7 +7749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7765,7 +7767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7783,7 +7785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7797,13 +7799,15 @@
       <c r="E6" s="62">
         <v>1</v>
       </c>
-      <c r="F6" s="63"/>
+      <c r="F6" s="63">
+        <v>0</v>
+      </c>
       <c r="G6" s="64">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -7821,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -7837,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -7855,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7877,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7893,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -7911,7 +7915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -7933,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -7955,7 +7959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -7977,7 +7981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -7999,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8017,7 +8021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8039,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>131</v>
       </c>
@@ -8059,7 +8063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>41</v>
       </c>
@@ -8079,7 +8083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>43</v>
       </c>
@@ -8099,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>283</v>
       </c>
@@ -8117,7 +8121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>45</v>
       </c>
@@ -8135,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>47</v>
       </c>
@@ -8157,7 +8161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -8175,7 +8179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -8193,7 +8197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -8226,7 +8230,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8236,8 +8240,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="87" t="s">
         <v>73</v>
       </c>
       <c r="B1" s="76"/>
@@ -8247,7 +8251,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8270,7 +8274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -8292,7 +8296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -8310,7 +8314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -8332,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -8350,7 +8354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -8372,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -8390,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -8410,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -8432,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -8454,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -8472,7 +8476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -8492,7 +8496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -8510,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>443</v>
       </c>
@@ -8532,7 +8536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>445</v>
       </c>
@@ -8548,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8570,7 +8574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8588,7 +8592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -8606,7 +8610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -8624,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -8642,7 +8646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -8660,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -8674,13 +8678,15 @@
       <c r="E23" s="62">
         <v>1</v>
       </c>
-      <c r="F23" s="63"/>
+      <c r="F23" s="63">
+        <v>1</v>
+      </c>
       <c r="G23" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -8698,7 +8704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -8729,7 +8735,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8739,7 +8745,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>74</v>
       </c>
@@ -8750,7 +8756,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8773,7 +8779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -8791,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -8809,7 +8815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -8827,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -8871,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -8889,7 +8895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -8907,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>27</v>
       </c>
@@ -8925,7 +8931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -8943,7 +8949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>31</v>
       </c>
@@ -8961,7 +8967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>33</v>
       </c>
@@ -8979,7 +8985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>37</v>
       </c>
@@ -8997,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>254</v>
       </c>
@@ -9019,7 +9025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52" t="s">
         <v>256</v>
       </c>
@@ -9035,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -9053,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -9075,7 +9081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -9097,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -9115,7 +9121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>49</v>
       </c>
@@ -9133,7 +9139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>51</v>
       </c>
@@ -9151,7 +9157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>53</v>
       </c>
@@ -9180,7 +9186,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9190,8 +9196,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="88" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="76"/>
@@ -9201,7 +9207,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9224,7 +9230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9246,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9264,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9282,7 +9288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9300,7 +9306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9318,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9338,7 +9344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -9356,7 +9362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -9378,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -9394,7 +9400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -9412,7 +9418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -9432,7 +9438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -9454,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -9472,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -9492,7 +9498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -9514,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -9536,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -9556,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -9574,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -9592,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -9614,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -9636,7 +9642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -9656,7 +9662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -9674,7 +9680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -9707,7 +9713,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9717,7 +9723,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="78" t="s">
         <v>59</v>
       </c>
@@ -9728,7 +9734,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9751,7 +9757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9773,7 +9779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9791,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9813,7 +9819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9831,7 +9837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9849,7 +9855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9867,7 +9873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -9885,7 +9891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -9901,7 +9907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -9919,7 +9925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -9937,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -9955,7 +9961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -9977,7 +9983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -9999,7 +10005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -10017,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -10035,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -10057,7 +10063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -10079,7 +10085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -10094,14 +10100,14 @@
         <v>2</v>
       </c>
       <c r="F20" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>106</v>
       </c>
@@ -10121,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>107</v>
       </c>
@@ -10139,7 +10145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -10154,14 +10160,14 @@
         <v>2</v>
       </c>
       <c r="F23" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -10176,14 +10182,14 @@
         <v>2</v>
       </c>
       <c r="F24" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>111</v>
       </c>
@@ -10210,7 +10216,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10220,8 +10226,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="76"/>
@@ -10231,7 +10237,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10254,7 +10260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10272,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10290,7 +10296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10308,7 +10314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10330,7 +10336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -10352,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -10374,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -10392,7 +10398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>149</v>
       </c>
@@ -10412,7 +10418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>95</v>
       </c>
@@ -10430,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>29</v>
       </c>
@@ -10452,7 +10458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>31</v>
       </c>
@@ -10470,7 +10476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>33</v>
       </c>
@@ -10488,7 +10494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>37</v>
       </c>
@@ -10506,7 +10512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>39</v>
       </c>
@@ -10524,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -10546,7 +10552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -10564,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -10586,7 +10592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="52" t="s">
         <v>165</v>
       </c>
@@ -10604,7 +10610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>47</v>
       </c>
@@ -10622,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>49</v>
       </c>
@@ -10640,7 +10646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>51</v>
       </c>
@@ -10656,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="52" t="s">
         <v>214</v>
       </c>
@@ -10674,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>520</v>
       </c>
@@ -10696,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>522</v>
       </c>
@@ -10727,7 +10733,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10737,8 +10743,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="90" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="76"/>
@@ -10748,7 +10754,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10771,7 +10777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10786,14 +10792,14 @@
         <v>2</v>
       </c>
       <c r="F3" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="40">
         <f t="shared" ref="G3:G26" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10807,13 +10813,15 @@
       <c r="E4" s="38">
         <v>1</v>
       </c>
-      <c r="F4" s="39"/>
+      <c r="F4" s="39">
+        <v>1</v>
+      </c>
       <c r="G4" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10835,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10851,7 +10859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>17</v>
       </c>
@@ -10869,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -10891,7 +10899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>117</v>
       </c>
@@ -10911,7 +10919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>119</v>
       </c>
@@ -10929,7 +10937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>531</v>
       </c>
@@ -10947,7 +10955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>533</v>
       </c>
@@ -10959,13 +10967,15 @@
       <c r="E12" s="38">
         <v>1</v>
       </c>
-      <c r="F12" s="39"/>
+      <c r="F12" s="39">
+        <v>1</v>
+      </c>
       <c r="G12" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>149</v>
       </c>
@@ -10985,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>95</v>
       </c>
@@ -11001,7 +11011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>29</v>
       </c>
@@ -11019,7 +11029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>31</v>
       </c>
@@ -11037,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>33</v>
       </c>
@@ -11055,7 +11065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>37</v>
       </c>
@@ -11073,7 +11083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>39</v>
       </c>
@@ -11095,7 +11105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>41</v>
       </c>
@@ -11113,7 +11123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>43</v>
       </c>
@@ -11131,7 +11141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>45</v>
       </c>
@@ -11153,7 +11163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>47</v>
       </c>
@@ -11171,7 +11181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -11189,7 +11199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -11207,7 +11217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -11221,10 +11231,12 @@
       <c r="E26" s="38">
         <v>1</v>
       </c>
-      <c r="F26" s="39"/>
+      <c r="F26" s="39">
+        <v>1</v>
+      </c>
       <c r="G26" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11238,7 +11250,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -11248,8 +11260,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
         <v>549</v>
       </c>
       <c r="B1" s="76"/>
@@ -11259,7 +11271,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
@@ -11282,7 +11294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>550</v>
       </c>
@@ -11300,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>552</v>
       </c>
@@ -11318,7 +11330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>554</v>
       </c>
@@ -11336,7 +11348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>556</v>
       </c>
@@ -11354,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>558</v>
       </c>
@@ -11372,7 +11384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>560</v>
       </c>
@@ -11390,7 +11402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>562</v>
       </c>
@@ -11408,7 +11420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>564</v>
       </c>
@@ -11426,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>566</v>
       </c>
@@ -11444,7 +11456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>568</v>
       </c>
@@ -11462,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>570</v>
       </c>
@@ -11480,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>572</v>
       </c>
@@ -11498,7 +11510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>574</v>
       </c>
@@ -11516,7 +11528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>576</v>
       </c>
@@ -11534,7 +11546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>578</v>
       </c>
@@ -11552,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>580</v>
       </c>
@@ -11570,7 +11582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>582</v>
       </c>
@@ -11588,7 +11600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>584</v>
       </c>
@@ -11606,7 +11618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>586</v>
       </c>
@@ -11624,7 +11636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>588</v>
       </c>
@@ -11642,7 +11654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>590</v>
       </c>
@@ -11660,7 +11672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>592</v>
       </c>
@@ -11678,7 +11690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>594</v>
       </c>
@@ -11696,7 +11708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>596</v>
       </c>
@@ -11714,7 +11726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>598</v>
       </c>
@@ -11732,7 +11744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="65" t="s">
         <v>600</v>
       </c>
@@ -11750,7 +11762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="58" t="s">
         <v>602</v>
       </c>
@@ -11768,7 +11780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="65" t="s">
         <v>604</v>
       </c>
@@ -11786,7 +11798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="58" t="s">
         <v>606</v>
       </c>
@@ -11804,7 +11816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="65" t="s">
         <v>608</v>
       </c>
@@ -11822,7 +11834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="58" t="s">
         <v>610</v>
       </c>
@@ -11840,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="65" t="s">
         <v>612</v>
       </c>
@@ -11858,7 +11870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="58" t="s">
         <v>614</v>
       </c>
@@ -11876,7 +11888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="65" t="s">
         <v>616</v>
       </c>
@@ -11894,7 +11906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="58" t="s">
         <v>618</v>
       </c>
@@ -11912,7 +11924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="65" t="s">
         <v>620</v>
       </c>
@@ -11930,7 +11942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="58" t="s">
         <v>622</v>
       </c>
@@ -11948,7 +11960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="65" t="s">
         <v>624</v>
       </c>
@@ -11966,7 +11978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="58" t="s">
         <v>626</v>
       </c>
@@ -11984,7 +11996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="65" t="s">
         <v>628</v>
       </c>
@@ -12013,7 +12025,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12023,8 +12035,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="92" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="76"/>
@@ -12034,7 +12046,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12057,7 +12069,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12075,7 +12087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12097,7 +12109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12119,7 +12131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12141,7 +12153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12163,7 +12175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12185,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12207,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12225,7 +12237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12243,7 +12255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12261,7 +12273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12279,7 +12291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12297,7 +12309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12315,7 +12327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12333,7 +12345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12362,7 +12374,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12372,8 +12384,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="93" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="76"/>
@@ -12383,7 +12395,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12406,7 +12418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12424,7 +12436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12446,7 +12458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12466,7 +12478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12484,7 +12496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12502,7 +12514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12520,7 +12532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12540,7 +12552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12558,7 +12570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12591,7 +12603,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12601,7 +12613,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="94" t="s">
         <v>80</v>
       </c>
@@ -12612,7 +12624,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12635,7 +12647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12657,7 +12669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12675,7 +12687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12693,7 +12705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12715,7 +12727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12733,7 +12745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12751,7 +12763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12769,7 +12781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12787,7 +12799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12805,7 +12817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12823,7 +12835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12841,7 +12853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12859,7 +12871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12881,7 +12893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12901,7 +12913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12919,7 +12931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>45</v>
       </c>
@@ -12937,7 +12949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>47</v>
       </c>
@@ -12959,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>49</v>
       </c>
@@ -12981,7 +12993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>51</v>
       </c>
@@ -12999,7 +13011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>53</v>
       </c>
@@ -13021,7 +13033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>670</v>
       </c>
@@ -13039,7 +13051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>672</v>
       </c>
@@ -13061,7 +13073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>674</v>
       </c>
@@ -13094,7 +13106,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13104,7 +13116,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="95" t="s">
         <v>81</v>
       </c>
@@ -13115,7 +13127,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13138,7 +13150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>676</v>
       </c>
@@ -13156,7 +13168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>677</v>
       </c>
@@ -13170,13 +13182,15 @@
       <c r="E4" s="22">
         <v>1</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="23">
+        <v>1</v>
+      </c>
       <c r="G4" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>678</v>
       </c>
@@ -13194,7 +13208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>679</v>
       </c>
@@ -13212,7 +13226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>680</v>
       </c>
@@ -13234,7 +13248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>681</v>
       </c>
@@ -13252,7 +13266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>682</v>
       </c>
@@ -13270,7 +13284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>683</v>
       </c>
@@ -13288,7 +13302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>684</v>
       </c>
@@ -13306,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>685</v>
       </c>
@@ -13324,7 +13338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>686</v>
       </c>
@@ -13342,7 +13356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>687</v>
       </c>
@@ -13356,13 +13370,15 @@
       <c r="E14" s="22">
         <v>1</v>
       </c>
-      <c r="F14" s="23"/>
+      <c r="F14" s="23">
+        <v>1</v>
+      </c>
       <c r="G14" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>688</v>
       </c>
@@ -13380,7 +13396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>689</v>
       </c>
@@ -13398,7 +13414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>690</v>
       </c>
@@ -13416,7 +13432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>691</v>
       </c>
@@ -13434,7 +13450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>692</v>
       </c>
@@ -13456,7 +13472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>693</v>
       </c>
@@ -13474,7 +13490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>694</v>
       </c>
@@ -13492,7 +13508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>695</v>
       </c>
@@ -13510,7 +13526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>696</v>
       </c>
@@ -13524,13 +13540,15 @@
       <c r="E23" s="22">
         <v>1</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="23">
+        <v>1</v>
+      </c>
       <c r="G23" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>697</v>
       </c>
@@ -13548,7 +13566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>698</v>
       </c>
@@ -13577,7 +13595,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13587,7 +13605,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="96" t="s">
         <v>82</v>
       </c>
@@ -13598,7 +13616,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13621,7 +13639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>699</v>
       </c>
@@ -13637,7 +13655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>701</v>
       </c>
@@ -13653,7 +13671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>703</v>
       </c>
@@ -13669,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>705</v>
       </c>
@@ -13685,7 +13703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>707</v>
       </c>
@@ -13701,7 +13719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>709</v>
       </c>
@@ -13717,7 +13735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>711</v>
       </c>
@@ -13733,7 +13751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>713</v>
       </c>
@@ -13749,7 +13767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>715</v>
       </c>
@@ -13767,7 +13785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>717</v>
       </c>
@@ -13783,7 +13801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>719</v>
       </c>
@@ -13799,7 +13817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>721</v>
       </c>
@@ -13815,7 +13833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>723</v>
       </c>
@@ -13833,7 +13851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>725</v>
       </c>
@@ -13849,7 +13867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>727</v>
       </c>
@@ -13876,7 +13894,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13886,7 +13904,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="97" t="s">
         <v>729</v>
       </c>
@@ -13897,7 +13915,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13920,7 +13938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>730</v>
       </c>
@@ -13938,7 +13956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>732</v>
       </c>
@@ -13956,7 +13974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>734</v>
       </c>
@@ -13974,7 +13992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>736</v>
       </c>
@@ -13996,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>738</v>
       </c>
@@ -14014,7 +14032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>740</v>
       </c>
@@ -14032,7 +14050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>742</v>
       </c>
@@ -14050,7 +14068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>744</v>
       </c>
@@ -14068,7 +14086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>746</v>
       </c>
@@ -14090,7 +14108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>748</v>
       </c>
@@ -14112,7 +14130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>750</v>
       </c>
@@ -14130,7 +14148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>752</v>
       </c>
@@ -14148,7 +14166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>754</v>
       </c>
@@ -14166,7 +14184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>756</v>
       </c>
@@ -14184,7 +14202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>758</v>
       </c>
@@ -14202,7 +14220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>760</v>
       </c>
@@ -14224,7 +14242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>762</v>
       </c>
@@ -14242,7 +14260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>764</v>
       </c>
@@ -14260,7 +14278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>766</v>
       </c>
@@ -14278,7 +14296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>768</v>
       </c>
@@ -14296,7 +14314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>770</v>
       </c>
@@ -14318,7 +14336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>772</v>
       </c>
@@ -14336,7 +14354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>774</v>
       </c>
@@ -14354,7 +14372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>776</v>
       </c>
@@ -14372,7 +14390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>778</v>
       </c>
@@ -14390,7 +14408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>780</v>
       </c>
@@ -14408,7 +14426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>782</v>
       </c>
@@ -14426,7 +14444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>784</v>
       </c>
@@ -14448,7 +14466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>786</v>
       </c>
@@ -14466,7 +14484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>788</v>
       </c>
@@ -14484,7 +14502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>790</v>
       </c>
@@ -14502,7 +14520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>792</v>
       </c>
@@ -14520,7 +14538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>794</v>
       </c>
@@ -14538,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>796</v>
       </c>
@@ -14556,7 +14574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>798</v>
       </c>
@@ -14578,7 +14596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>800</v>
       </c>
@@ -14600,7 +14618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>802</v>
       </c>
@@ -14618,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>804</v>
       </c>
@@ -14636,7 +14654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
         <v>806</v>
       </c>
@@ -14654,7 +14672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>808</v>
       </c>
@@ -14672,7 +14690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
         <v>810</v>
       </c>
@@ -14690,7 +14708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>812</v>
       </c>
@@ -14708,7 +14726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
         <v>814</v>
       </c>
@@ -14726,7 +14744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>816</v>
       </c>
@@ -14744,7 +14762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
         <v>818</v>
       </c>
@@ -14762,7 +14780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
         <v>820</v>
       </c>
@@ -14780,7 +14798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
         <v>822</v>
       </c>
@@ -14798,7 +14816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
         <v>824</v>
       </c>
@@ -14820,7 +14838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
         <v>826</v>
       </c>
@@ -14838,7 +14856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>828</v>
       </c>
@@ -14856,7 +14874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
         <v>830</v>
       </c>
@@ -14878,7 +14896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>832</v>
       </c>
@@ -14896,7 +14914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
         <v>834</v>
       </c>
@@ -14914,7 +14932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>836</v>
       </c>
@@ -14936,7 +14954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
         <v>838</v>
       </c>
@@ -14958,7 +14976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>840</v>
       </c>
@@ -14976,7 +14994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
         <v>842</v>
       </c>
@@ -14998,7 +15016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="25" t="s">
         <v>844</v>
       </c>
@@ -15016,7 +15034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>846</v>
       </c>
@@ -15034,7 +15052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="25" t="s">
         <v>848</v>
       </c>
@@ -15056,7 +15074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
         <v>850</v>
       </c>
@@ -15072,7 +15090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="25" t="s">
         <v>852</v>
       </c>
@@ -15090,7 +15108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>854</v>
       </c>
@@ -15106,7 +15124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="25" t="s">
         <v>856</v>
       </c>
@@ -15126,7 +15144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
         <v>858</v>
       </c>
@@ -15144,7 +15162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
         <v>860</v>
       </c>
@@ -15160,7 +15178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
         <v>862</v>
       </c>
@@ -15178,7 +15196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
         <v>864</v>
       </c>
@@ -15194,7 +15212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
         <v>866</v>
       </c>
@@ -15210,7 +15228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
         <v>868</v>
       </c>
@@ -15230,7 +15248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
         <v>870</v>
       </c>
@@ -15246,7 +15264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
         <v>872</v>
       </c>
@@ -15266,7 +15284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
         <v>874</v>
       </c>
@@ -15282,7 +15300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="25" t="s">
         <v>876</v>
       </c>
@@ -15298,7 +15316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
         <v>878</v>
       </c>
@@ -15314,7 +15332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="25" t="s">
         <v>880</v>
       </c>
@@ -15330,7 +15348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
         <v>882</v>
       </c>
@@ -15348,7 +15366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="25" t="s">
         <v>884</v>
       </c>
@@ -15364,7 +15382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
         <v>886</v>
       </c>
@@ -15384,7 +15402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="25" t="s">
         <v>888</v>
       </c>
@@ -15415,7 +15433,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15425,7 +15443,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>60</v>
       </c>
@@ -15436,7 +15454,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15459,7 +15477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -15477,7 +15495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -15497,7 +15515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -15515,7 +15533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -15537,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -15555,7 +15573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>117</v>
       </c>
@@ -15571,7 +15589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>119</v>
       </c>
@@ -15593,7 +15611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -15615,7 +15633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -15637,7 +15655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -15655,7 +15673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -15671,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -15693,7 +15711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -15715,7 +15733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -15737,7 +15755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>39</v>
       </c>
@@ -15753,7 +15771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>131</v>
       </c>
@@ -15771,7 +15789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -15789,7 +15807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -15811,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -15833,7 +15851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>136</v>
       </c>
@@ -15853,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>138</v>
       </c>
@@ -15875,7 +15893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -15897,7 +15915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -15919,7 +15937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -15933,10 +15951,12 @@
       <c r="E26" s="38">
         <v>2</v>
       </c>
-      <c r="F26" s="39"/>
+      <c r="F26" s="39">
+        <v>2</v>
+      </c>
       <c r="G26" s="40">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15950,7 +15970,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15960,7 +15980,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>61</v>
       </c>
@@ -15971,7 +15991,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15994,7 +16014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16012,7 +16032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16030,7 +16050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16048,7 +16068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16066,7 +16086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16084,7 +16104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -16100,7 +16120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -16122,7 +16142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>149</v>
       </c>
@@ -16140,7 +16160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -16160,7 +16180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16178,7 +16198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16198,7 +16218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -16216,7 +16236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -16238,7 +16258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -16260,7 +16280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -16282,7 +16302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>159</v>
       </c>
@@ -16304,7 +16324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>161</v>
       </c>
@@ -16324,7 +16344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -16346,7 +16366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -16366,7 +16386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>165</v>
       </c>
@@ -16384,7 +16404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -16402,7 +16422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>49</v>
       </c>
@@ -16420,7 +16440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
@@ -16438,7 +16458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -16467,7 +16487,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16477,7 +16497,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="80" t="s">
         <v>62</v>
       </c>
@@ -16488,7 +16508,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16511,7 +16531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16529,7 +16549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16551,7 +16571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16569,7 +16589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16591,7 +16611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16609,7 +16629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>117</v>
       </c>
@@ -16629,7 +16649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>119</v>
       </c>
@@ -16647,7 +16667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -16665,7 +16685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -16683,7 +16703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16705,7 +16725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16727,7 +16747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -16749,7 +16769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -16771,7 +16791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -16789,7 +16809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -16807,7 +16827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -16825,7 +16845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -16843,7 +16863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -16861,7 +16881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>49</v>
       </c>
@@ -16881,7 +16901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>188</v>
       </c>
@@ -16899,7 +16919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -16917,7 +16937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -16946,7 +16966,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16956,7 +16976,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
@@ -16967,7 +16987,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16990,7 +17010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17008,7 +17028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17026,7 +17046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17044,7 +17064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17060,7 +17080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>17</v>
       </c>
@@ -17078,7 +17098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>19</v>
       </c>
@@ -17094,7 +17114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>21</v>
       </c>
@@ -17116,7 +17136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>23</v>
       </c>
@@ -17134,7 +17154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>25</v>
       </c>
@@ -17152,7 +17172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>27</v>
       </c>
@@ -17174,7 +17194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>29</v>
       </c>
@@ -17192,7 +17212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -17210,7 +17230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -17230,7 +17250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
@@ -17248,7 +17268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -17266,7 +17286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -17277,18 +17297,14 @@
       <c r="D18" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="62">
-        <v>2</v>
-      </c>
-      <c r="F18" s="63">
-        <v>1</v>
-      </c>
+      <c r="E18" s="62"/>
+      <c r="F18" s="63"/>
       <c r="G18" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -17310,7 +17326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -17332,7 +17348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -17354,7 +17370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -17376,7 +17392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -17398,7 +17414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17416,7 +17432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -17445,7 +17461,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17455,7 +17471,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="82" t="s">
         <v>63</v>
       </c>
@@ -17466,7 +17482,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17489,7 +17505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17507,7 +17523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17525,7 +17541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17543,7 +17559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17565,7 +17581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -17583,7 +17599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -17601,7 +17617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -17623,7 +17639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -17641,7 +17657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>123</v>
       </c>
@@ -17659,7 +17675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>125</v>
       </c>
@@ -17679,7 +17695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -17697,7 +17713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -17715,7 +17731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -17737,7 +17753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -17759,7 +17775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -17781,7 +17797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>206</v>
       </c>
@@ -17797,7 +17813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -17813,7 +17829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -17831,7 +17847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -17849,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>106</v>
       </c>
@@ -17871,7 +17887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>107</v>
       </c>
@@ -17887,7 +17903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17909,7 +17925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -17925,7 +17941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -17954,7 +17970,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17964,7 +17980,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>64</v>
       </c>
@@ -17975,7 +17991,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17998,7 +18014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -18020,7 +18036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -18038,7 +18054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -18056,7 +18072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -18074,7 +18090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -18092,7 +18108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -18110,7 +18126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -18132,7 +18148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -18154,7 +18170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>224</v>
       </c>
@@ -18170,7 +18186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>123</v>
       </c>
@@ -18192,7 +18208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>125</v>
       </c>
@@ -18212,7 +18228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -18230,7 +18246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -18248,7 +18264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -18266,7 +18282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -18284,7 +18300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -18302,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>206</v>
       </c>
@@ -18318,7 +18334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -18336,7 +18352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -18358,7 +18374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -18376,7 +18392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -18398,7 +18414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -18416,7 +18432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -18449,7 +18465,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -18459,7 +18475,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="84" t="s">
         <v>65</v>
       </c>
@@ -18470,7 +18486,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18493,7 +18509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -18511,7 +18527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="52" t="s">
         <v>11</v>
       </c>
@@ -18527,7 +18543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>241</v>
       </c>
@@ -18545,7 +18561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -18567,7 +18583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>15</v>
       </c>
@@ -18585,7 +18601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -18601,7 +18617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>23</v>
       </c>
@@ -18619,7 +18635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -18637,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -18653,7 +18669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -18673,7 +18689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -18691,7 +18707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -18713,7 +18729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -18735,7 +18751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -18753,7 +18769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
@@ -18775,7 +18791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>256</v>
       </c>
@@ -18791,7 +18807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -18813,7 +18829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -18835,7 +18851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -18857,7 +18873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -18875,7 +18891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>49</v>
       </c>
@@ -18893,7 +18909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>51</v>
       </c>
@@ -18915,7 +18931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>53</v>
       </c>

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FD8E0D-921B-413B-8016-E99634A8B675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3B5F34-CAF7-48C1-A4A7-CBA898FD3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="18" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,9 +3400,6 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3426,6 +3423,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3777,15 +3777,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3819,11 +3819,11 @@
       </c>
       <c r="C3" s="4">
         <f>COUNTIF('D. ALAVÉS'!C3:C25,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="5">
         <f>COUNTIF('D. ALAVÉS'!D3:D25,"X")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="6">
         <f>SUMIF('D. ALAVÉS'!E3:E25,"&gt;"&amp;0,'D. ALAVÉS'!E3:E25)</f>
@@ -4015,11 +4015,11 @@
       </c>
       <c r="C10" s="4">
         <f>COUNTIF('ELCHE CF'!C3:C25,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5">
         <f>COUNTIF('ELCHE CF'!D3:D25,"X")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="6">
         <f>SUMIF('ELCHE CF'!E3:E25,"&gt;"&amp;0,'ELCHE CF'!E3:E25)</f>
@@ -4071,11 +4071,11 @@
       </c>
       <c r="C12" s="4">
         <f>COUNTIF('GETAFE CF'!C3:C23,"")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5">
         <f>COUNTIF('GETAFE CF'!D3:D23,"X")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="6">
         <f>SUMIF('GETAFE CF'!E3:E23,"&gt;"&amp;0,'GETAFE CF'!E3:E23)</f>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="C13" s="4">
         <f>COUNTIF('LEVANTE UD'!C3:C26,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5">
         <f>COUNTIF('LEVANTE UD'!D3:D26,"X")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" s="6">
         <f>SUMIF('LEVANTE UD'!E3:E26,"&gt;"&amp;0,'LEVANTE UD'!E3:E26)</f>
@@ -4155,11 +4155,11 @@
       </c>
       <c r="C15" s="4">
         <f>COUNTIF('MÁLAGA CF'!C3:C24,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5">
         <f>COUNTIF('MÁLAGA CF'!D3:D24,"X")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6">
         <f>SUMIF('MÁLAGA CF'!E3:E24,"&gt;"&amp;0,'MÁLAGA CF'!E3:E24)</f>
@@ -4239,19 +4239,19 @@
       </c>
       <c r="C18" s="4">
         <f>COUNTIF('RAYO VALLECANO'!C3:C25,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="5">
         <f>COUNTIF('RAYO VALLECANO'!D3:D25,"X")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="6">
         <f>SUMIF('RAYO VALLECANO'!E3:E25,"&gt;"&amp;0,'RAYO VALLECANO'!E3:E25)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="7">
         <f>SUM('RAYO VALLECANO'!F3:F25)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="8">
         <f>SUM('RAYO VALLECANO'!G3:G25)</f>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="C21" s="4">
         <f>COUNTIF('VALENCIA CF'!C3:C26,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="5">
         <f>COUNTIF('VALENCIA CF'!D3:D26,"X")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="6">
         <f>SUMIF('VALENCIA CF'!E3:E26,"&gt;"&amp;0,'VALENCIA CF'!E3:E26)</f>
@@ -4379,11 +4379,11 @@
       </c>
       <c r="C23" s="4">
         <f>COUNTIF('ADN - LALIGA PRIME'!C3:C17,"")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5">
         <f>COUNTIF('ADN - LALIGA PRIME'!D3:D17,"X")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="6">
         <f>SUMIF('ADN - LALIGA PRIME'!E3:E17,"&gt;"&amp;0,'ADN - LALIGA PRIME'!E3:E17)</f>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="C29" s="29">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!C3:C42,"")</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D29" s="30">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!D3:D42,"X")</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E29" s="31">
         <f>SUMIF('ÚLTIMOS FICHAJES'!E3:E42,"&gt;"&amp;0,'ÚLTIMOS FICHAJES'!E3:E42)</f>
@@ -4576,19 +4576,19 @@
       </c>
       <c r="C30" s="13">
         <f t="shared" si="0"/>
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E30" s="15">
         <f t="shared" si="0"/>
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
@@ -4596,13 +4596,13 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
@@ -4632,15 +4632,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5145,15 +5145,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5437,10 +5437,10 @@
       <c r="B16" s="66" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="61"/>
       <c r="E16" s="62"/>
       <c r="F16" s="63"/>
       <c r="G16" s="64">
@@ -5473,10 +5473,10 @@
       <c r="B18" s="66" t="s">
         <v>304</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="61"/>
       <c r="E18" s="62"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64">
@@ -5603,12 +5603,12 @@
       <c r="A1" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5898,10 +5898,10 @@
       <c r="B16" s="66" t="s">
         <v>322</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="61"/>
       <c r="E16" s="62">
         <v>1</v>
       </c>
@@ -6128,12 +6128,12 @@
       <c r="A1" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6700,15 +6700,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -6942,10 +6942,10 @@
       <c r="B13" s="59" t="s">
         <v>374</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C13" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="61"/>
       <c r="E13" s="62"/>
       <c r="F13" s="63"/>
       <c r="G13" s="64">
@@ -7195,15 +7195,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -7698,15 +7698,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -8244,12 +8244,12 @@
       <c r="A1" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -8671,16 +8671,12 @@
       <c r="B23" s="59" t="s">
         <v>453</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="62">
-        <v>1</v>
-      </c>
-      <c r="F23" s="63">
-        <v>1</v>
-      </c>
+      <c r="C23" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="61"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="63"/>
       <c r="G23" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8746,15 +8742,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9200,12 +9196,12 @@
       <c r="A1" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9724,15 +9720,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -9786,10 +9782,10 @@
       <c r="B4" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="61"/>
       <c r="E4" s="62"/>
       <c r="F4" s="63"/>
       <c r="G4" s="64">
@@ -10230,12 +10226,12 @@
       <c r="A1" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -10559,10 +10555,10 @@
       <c r="B18" s="42" t="s">
         <v>513</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C18" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="37"/>
       <c r="E18" s="38"/>
       <c r="F18" s="39"/>
       <c r="G18" s="40">
@@ -10747,12 +10743,12 @@
       <c r="A1" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -11264,12 +11260,12 @@
       <c r="A1" s="91" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
@@ -11319,10 +11315,10 @@
       <c r="B4" s="66" t="s">
         <v>553</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C4" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="61"/>
       <c r="E4" s="62"/>
       <c r="F4" s="63"/>
       <c r="G4" s="64">
@@ -11355,10 +11351,10 @@
       <c r="B6" s="66" t="s">
         <v>557</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C6" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="61"/>
       <c r="E6" s="62"/>
       <c r="F6" s="63"/>
       <c r="G6" s="64">
@@ -11373,10 +11369,10 @@
       <c r="B7" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C7" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="61"/>
       <c r="E7" s="62"/>
       <c r="F7" s="63"/>
       <c r="G7" s="64">
@@ -11409,10 +11405,10 @@
       <c r="B9" s="59" t="s">
         <v>563</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C9" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="61"/>
       <c r="E9" s="62"/>
       <c r="F9" s="63"/>
       <c r="G9" s="64">
@@ -11445,10 +11441,10 @@
       <c r="B11" s="59" t="s">
         <v>567</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C11" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="61"/>
       <c r="E11" s="62"/>
       <c r="F11" s="63"/>
       <c r="G11" s="64">
@@ -11517,10 +11513,10 @@
       <c r="B15" s="59" t="s">
         <v>575</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C15" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="61"/>
       <c r="E15" s="62"/>
       <c r="F15" s="63"/>
       <c r="G15" s="64">
@@ -12039,12 +12035,12 @@
       <c r="A1" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12226,10 +12222,10 @@
       <c r="B10" s="26" t="s">
         <v>637</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="23"/>
       <c r="G10" s="24">
@@ -12334,10 +12330,10 @@
       <c r="B16" s="26" t="s">
         <v>643</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="21"/>
       <c r="E16" s="22"/>
       <c r="F16" s="23"/>
       <c r="G16" s="24">
@@ -12388,12 +12384,12 @@
       <c r="A1" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -12617,12 +12613,12 @@
       <c r="A1" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13120,12 +13116,12 @@
       <c r="A1" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13609,12 +13605,12 @@
       <c r="A1" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13908,12 +13904,12 @@
       <c r="A1" s="97" t="s">
         <v>729</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15444,15 +15440,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15981,15 +15977,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16498,15 +16494,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -16977,15 +16973,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="A1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -17472,15 +17468,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -17981,15 +17977,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -18476,15 +18472,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -18550,10 +18546,10 @@
       <c r="B5" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="47" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="47"/>
       <c r="E5" s="45"/>
       <c r="F5" s="46"/>
       <c r="G5" s="40">

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3B5F34-CAF7-48C1-A4A7-CBA898FD3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3581BB-6412-4C8B-8AC5-016DBFEF5BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="18" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,6 +3400,9 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3447,9 +3450,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3770,24 +3770,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>60</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -3943,14 +3943,14 @@
       </c>
       <c r="F7" s="7">
         <f>SUM('REAL BETIS'!F3:F25)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="8">
         <f>SUM('REAL BETIS'!G3:G25)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>63</v>
       </c>
@@ -3971,14 +3971,14 @@
       </c>
       <c r="F8" s="7">
         <f>SUM('RC CELTA DE VIGO'!F3:F26)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="8">
         <f>SUM('RC CELTA DE VIGO'!G3:G26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>65</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -4055,14 +4055,14 @@
       </c>
       <c r="F11" s="7">
         <f>SUM('RCD ESPANYOL'!F3:F25)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" s="8">
         <f>SUM('RCD ESPANYOL'!G3:G25)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>67</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>68</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>69</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
@@ -4167,14 +4167,14 @@
       </c>
       <c r="F15" s="7">
         <f>SUM('MÁLAGA CF'!F3:F24)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="8">
         <f>SUM('MÁLAGA CF'!G3:G24)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>71</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -4223,14 +4223,14 @@
       </c>
       <c r="F17" s="7">
         <f>SUM('R. RACING CLUB'!F3:F27)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="8">
         <f>SUM('R. RACING CLUB'!G3:G27)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>73</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>74</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>77</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>78</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>79</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>81</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>83</v>
       </c>
@@ -4531,14 +4531,14 @@
       </c>
       <c r="F28" s="7">
         <f>SUM('CHICLE LIGA 2627'!F3:F82)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G28" s="8">
         <f>SUM('CHICLE LIGA 2627'!G3:G82)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>84</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>85</v>
       </c>
@@ -4588,23 +4588,23 @@
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
         <v>86</v>
       </c>
@@ -4621,7 +4621,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4631,18 +4631,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>275</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -4922,14 +4922,14 @@
         <v>2</v>
       </c>
       <c r="F15" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>283</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -5134,7 +5134,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5144,18 +5144,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>29</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>33</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>37</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>39</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>41</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>43</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>45</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>47</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>49</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>51</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>214</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>53</v>
       </c>
@@ -5589,7 +5589,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5599,18 +5599,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>159</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>161</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>111</v>
       </c>
@@ -6114,7 +6114,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6124,18 +6124,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>343</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>345</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>351</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>353</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>355</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>357</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>360</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -6689,7 +6689,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6699,18 +6699,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6906,14 +6906,14 @@
         <v>3</v>
       </c>
       <c r="F11" s="63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>49</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -7184,7 +7184,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7194,18 +7194,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>19</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>21</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>23</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -7426,7 +7426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -7687,7 +7687,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7697,18 +7697,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7800,14 +7800,14 @@
         <v>1</v>
       </c>
       <c r="F6" s="63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -7981,7 +7981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>131</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>41</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>43</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>283</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>45</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>47</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -8230,7 +8230,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8240,18 +8240,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>443</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>445</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -8731,7 +8731,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8741,18 +8741,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>27</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>31</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>33</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>37</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>254</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
         <v>256</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>49</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>51</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>53</v>
       </c>
@@ -9182,7 +9182,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9192,18 +9192,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -9358,7 +9358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -9709,7 +9709,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9719,18 +9719,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>106</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>107</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>111</v>
       </c>
@@ -10212,7 +10212,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10222,18 +10222,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>149</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>95</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>29</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>31</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>33</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>37</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>39</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
         <v>165</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>47</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>49</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>51</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="52" t="s">
         <v>214</v>
       </c>
@@ -10676,7 +10676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>520</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>522</v>
       </c>
@@ -10729,7 +10729,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10739,18 +10739,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>17</v>
       </c>
@@ -10873,7 +10873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -10895,7 +10895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>117</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>119</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>531</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>533</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>149</v>
       </c>
@@ -10991,7 +10991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>95</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>29</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>31</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>33</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>37</v>
       </c>
@@ -11079,7 +11079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>39</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>41</v>
       </c>
@@ -11119,7 +11119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>43</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>45</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>47</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -11195,7 +11195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -11246,7 +11246,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -11256,18 +11256,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="92" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>550</v>
       </c>
@@ -11308,7 +11308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>552</v>
       </c>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>554</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>556</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>558</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>560</v>
       </c>
@@ -11398,7 +11398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>562</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>564</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>566</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>568</v>
       </c>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>570</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>572</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>574</v>
       </c>
@@ -11524,7 +11524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>576</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>578</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>580</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>582</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>584</v>
       </c>
@@ -11614,7 +11614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>586</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>588</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>590</v>
       </c>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>592</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>594</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>596</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>598</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="65" t="s">
         <v>600</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58" t="s">
         <v>602</v>
       </c>
@@ -11776,7 +11776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
         <v>604</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58" t="s">
         <v>606</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65" t="s">
         <v>608</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58" t="s">
         <v>610</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="65" t="s">
         <v>612</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58" t="s">
         <v>614</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="65" t="s">
         <v>616</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
         <v>618</v>
       </c>
@@ -11920,7 +11920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="65" t="s">
         <v>620</v>
       </c>
@@ -11938,7 +11938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58" t="s">
         <v>622</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="65" t="s">
         <v>624</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
         <v>626</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="65" t="s">
         <v>628</v>
       </c>
@@ -12021,7 +12021,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12031,18 +12031,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12149,7 +12149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12215,7 +12215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12323,7 +12323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12370,7 +12370,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12380,18 +12380,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12454,7 +12454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12599,7 +12599,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12609,18 +12609,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12643,7 +12643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12665,7 +12665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12701,7 +12701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12889,7 +12889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>45</v>
       </c>
@@ -12945,7 +12945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>47</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>49</v>
       </c>
@@ -12989,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>51</v>
       </c>
@@ -13007,7 +13007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>53</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>670</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>672</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>674</v>
       </c>
@@ -13102,7 +13102,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13112,18 +13112,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>676</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>677</v>
       </c>
@@ -13186,7 +13186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>678</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>679</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>680</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>681</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>682</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>683</v>
       </c>
@@ -13298,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>684</v>
       </c>
@@ -13316,7 +13316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>685</v>
       </c>
@@ -13334,7 +13334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>686</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>687</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>688</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>689</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>690</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>691</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>692</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>693</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>694</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>695</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>696</v>
       </c>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>697</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>698</v>
       </c>
@@ -13591,7 +13591,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13601,18 +13601,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>699</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>701</v>
       </c>
@@ -13667,7 +13667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>703</v>
       </c>
@@ -13683,7 +13683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>705</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>707</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>709</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>711</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>713</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>715</v>
       </c>
@@ -13781,7 +13781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>717</v>
       </c>
@@ -13797,7 +13797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>719</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>721</v>
       </c>
@@ -13829,7 +13829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>723</v>
       </c>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>725</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>727</v>
       </c>
@@ -13890,7 +13890,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13900,18 +13900,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="97" t="s">
         <v>729</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13934,7 +13934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>730</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>732</v>
       </c>
@@ -13970,7 +13970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>734</v>
       </c>
@@ -13988,7 +13988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>736</v>
       </c>
@@ -14010,7 +14010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>738</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>740</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>742</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>744</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>746</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>748</v>
       </c>
@@ -14126,7 +14126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>750</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>752</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>754</v>
       </c>
@@ -14180,7 +14180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>756</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>758</v>
       </c>
@@ -14216,7 +14216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>760</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>762</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>764</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>766</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>768</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>770</v>
       </c>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>772</v>
       </c>
@@ -14350,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>774</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>776</v>
       </c>
@@ -14386,7 +14386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>778</v>
       </c>
@@ -14404,7 +14404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>780</v>
       </c>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>782</v>
       </c>
@@ -14440,7 +14440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>784</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>786</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>788</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>790</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
         <v>792</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>794</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>796</v>
       </c>
@@ -14570,7 +14570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>798</v>
       </c>
@@ -14592,7 +14592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>800</v>
       </c>
@@ -14614,7 +14614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
         <v>802</v>
       </c>
@@ -14632,7 +14632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>804</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>806</v>
       </c>
@@ -14668,7 +14668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
         <v>808</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>810</v>
       </c>
@@ -14704,7 +14704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
         <v>812</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>814</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="25" t="s">
         <v>816</v>
       </c>
@@ -14758,7 +14758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>818</v>
       </c>
@@ -14776,7 +14776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="25" t="s">
         <v>820</v>
       </c>
@@ -14794,7 +14794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>822</v>
       </c>
@@ -14812,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="25" t="s">
         <v>824</v>
       </c>
@@ -14834,7 +14834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
         <v>826</v>
       </c>
@@ -14852,7 +14852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="25" t="s">
         <v>828</v>
       </c>
@@ -14870,7 +14870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>830</v>
       </c>
@@ -14892,7 +14892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="25" t="s">
         <v>832</v>
       </c>
@@ -14910,7 +14910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>834</v>
       </c>
@@ -14928,7 +14928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
         <v>836</v>
       </c>
@@ -14950,7 +14950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>838</v>
       </c>
@@ -14972,7 +14972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="25" t="s">
         <v>840</v>
       </c>
@@ -14990,7 +14990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
         <v>842</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="25" t="s">
         <v>844</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
         <v>846</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
         <v>848</v>
       </c>
@@ -15070,7 +15070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>850</v>
       </c>
@@ -15086,7 +15086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
         <v>852</v>
       </c>
@@ -15098,13 +15098,15 @@
       <c r="E64" s="22">
         <v>2</v>
       </c>
-      <c r="F64" s="23"/>
+      <c r="F64" s="23">
+        <v>1</v>
+      </c>
       <c r="G64" s="24">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>854</v>
       </c>
@@ -15120,7 +15122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
         <v>856</v>
       </c>
@@ -15140,7 +15142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>858</v>
       </c>
@@ -15152,13 +15154,15 @@
       <c r="E67" s="22">
         <v>1</v>
       </c>
-      <c r="F67" s="23"/>
+      <c r="F67" s="23">
+        <v>1</v>
+      </c>
       <c r="G67" s="24">
         <f t="shared" ref="G67:G82" si="2">MAX(0,IF(E67="",0,E67)-IF(F67="",0,F67))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
         <v>860</v>
       </c>
@@ -15174,7 +15178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
         <v>862</v>
       </c>
@@ -15192,7 +15196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
         <v>864</v>
       </c>
@@ -15208,7 +15212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
         <v>866</v>
       </c>
@@ -15224,7 +15228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
         <v>868</v>
       </c>
@@ -15244,7 +15248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
         <v>870</v>
       </c>
@@ -15260,7 +15264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
         <v>872</v>
       </c>
@@ -15280,7 +15284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
         <v>874</v>
       </c>
@@ -15296,7 +15300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
         <v>876</v>
       </c>
@@ -15312,7 +15316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
         <v>878</v>
       </c>
@@ -15328,7 +15332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="25" t="s">
         <v>880</v>
       </c>
@@ -15344,7 +15348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
         <v>882</v>
       </c>
@@ -15362,7 +15366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="25" t="s">
         <v>884</v>
       </c>
@@ -15378,7 +15382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
         <v>886</v>
       </c>
@@ -15398,7 +15402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="25" t="s">
         <v>888</v>
       </c>
@@ -15429,7 +15433,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15439,18 +15443,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15473,7 +15477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -15491,7 +15495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -15511,7 +15515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -15529,7 +15533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -15551,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -15569,7 +15573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>117</v>
       </c>
@@ -15585,7 +15589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>119</v>
       </c>
@@ -15607,7 +15611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -15629,7 +15633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -15651,7 +15655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -15669,7 +15673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -15685,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -15707,7 +15711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -15729,7 +15733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -15751,7 +15755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>39</v>
       </c>
@@ -15767,7 +15771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>131</v>
       </c>
@@ -15785,7 +15789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -15803,7 +15807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -15825,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -15847,7 +15851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>136</v>
       </c>
@@ -15867,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>138</v>
       </c>
@@ -15889,7 +15893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -15911,7 +15915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -15933,7 +15937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -15966,7 +15970,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15976,18 +15980,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16010,7 +16014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16028,7 +16032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16046,7 +16050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16064,7 +16068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16082,7 +16086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16100,7 +16104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -16116,7 +16120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -16138,7 +16142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>149</v>
       </c>
@@ -16156,7 +16160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -16176,7 +16180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16194,7 +16198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16214,7 +16218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -16232,7 +16236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -16254,7 +16258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -16276,7 +16280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -16298,7 +16302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>159</v>
       </c>
@@ -16320,7 +16324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>161</v>
       </c>
@@ -16340,7 +16344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -16362,7 +16366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -16382,7 +16386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>165</v>
       </c>
@@ -16400,7 +16404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -16418,7 +16422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>49</v>
       </c>
@@ -16436,7 +16440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
@@ -16454,7 +16458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -16483,7 +16487,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16493,18 +16497,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16527,7 +16531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16545,7 +16549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16567,7 +16571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16585,7 +16589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16607,7 +16611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16625,7 +16629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>117</v>
       </c>
@@ -16645,7 +16649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>119</v>
       </c>
@@ -16663,7 +16667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -16681,7 +16685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -16699,7 +16703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16721,7 +16725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16743,7 +16747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -16765,7 +16769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -16787,7 +16791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -16805,7 +16809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -16823,7 +16827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -16841,7 +16845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -16859,7 +16863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -16877,7 +16881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>49</v>
       </c>
@@ -16897,7 +16901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>188</v>
       </c>
@@ -16915,7 +16919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -16933,7 +16937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -16962,7 +16966,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16972,18 +16976,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17006,7 +17010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17024,7 +17028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17042,7 +17046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17060,7 +17064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17076,7 +17080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>17</v>
       </c>
@@ -17094,7 +17098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>19</v>
       </c>
@@ -17110,7 +17114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>21</v>
       </c>
@@ -17132,7 +17136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>23</v>
       </c>
@@ -17150,7 +17154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>25</v>
       </c>
@@ -17168,7 +17172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>27</v>
       </c>
@@ -17190,7 +17194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>29</v>
       </c>
@@ -17208,7 +17212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -17226,7 +17230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -17246,7 +17250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
@@ -17264,7 +17268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -17282,7 +17286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -17300,7 +17304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -17315,14 +17319,14 @@
         <v>2</v>
       </c>
       <c r="F19" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -17344,7 +17348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -17366,7 +17370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -17388,7 +17392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -17410,7 +17414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17428,7 +17432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -17457,7 +17461,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17467,18 +17471,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17501,7 +17505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17519,7 +17523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17537,7 +17541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17555,7 +17559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17577,7 +17581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -17595,7 +17599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -17613,7 +17617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -17635,7 +17639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -17653,7 +17657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>123</v>
       </c>
@@ -17671,7 +17675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>125</v>
       </c>
@@ -17691,7 +17695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -17709,7 +17713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -17727,7 +17731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -17749,7 +17753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -17771,7 +17775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -17793,7 +17797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>206</v>
       </c>
@@ -17809,7 +17813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -17825,7 +17829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -17843,7 +17847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -17861,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>106</v>
       </c>
@@ -17883,7 +17887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>107</v>
       </c>
@@ -17899,7 +17903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17914,14 +17918,14 @@
         <v>2</v>
       </c>
       <c r="F24" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -17937,7 +17941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -17966,7 +17970,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17976,18 +17980,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18010,7 +18014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -18032,7 +18036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -18050,7 +18054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -18068,7 +18072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -18086,7 +18090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -18104,7 +18108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -18122,7 +18126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -18144,7 +18148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -18166,7 +18170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>224</v>
       </c>
@@ -18182,7 +18186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>123</v>
       </c>
@@ -18204,7 +18208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>125</v>
       </c>
@@ -18224,7 +18228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -18242,7 +18246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -18260,7 +18264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -18278,7 +18282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -18296,7 +18300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -18314,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
         <v>206</v>
       </c>
@@ -18330,7 +18334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -18348,7 +18352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -18370,7 +18374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -18388,7 +18392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -18410,7 +18414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -18428,7 +18432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -18461,7 +18465,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -18471,18 +18475,18 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18505,7 +18509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -18523,7 +18527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
         <v>11</v>
       </c>
@@ -18539,7 +18543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>241</v>
       </c>
@@ -18557,7 +18561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -18579,7 +18583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>15</v>
       </c>
@@ -18597,7 +18601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -18613,7 +18617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>23</v>
       </c>
@@ -18631,7 +18635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -18649,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -18665,7 +18669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -18685,7 +18689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -18703,7 +18707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -18725,7 +18729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -18747,7 +18751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -18765,7 +18769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
@@ -18787,7 +18791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>256</v>
       </c>
@@ -18803,7 +18807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -18825,7 +18829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -18847,7 +18851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -18869,7 +18873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -18887,7 +18891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>49</v>
       </c>
@@ -18905,7 +18909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>51</v>
       </c>
@@ -18927,7 +18931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>53</v>
       </c>

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3581BB-6412-4C8B-8AC5-016DBFEF5BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20004C6A-6932-4FDE-BEC0-9525278AAB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3452,6 +3452,9 @@
     <xf numFmtId="0" fontId="13" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3462,9 +3465,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3770,13 +3770,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>55</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>60</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>62</v>
       </c>
@@ -3915,14 +3915,14 @@
       </c>
       <c r="F6" s="7">
         <f>SUM('FC BARCELONA'!F3:F24)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="8">
         <f>SUM('FC BARCELONA'!G3:G24)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>63</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>65</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>67</v>
       </c>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="F12" s="7">
         <f>SUM('GETAFE CF'!F3:F23)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="8">
         <f>SUM('GETAFE CF'!G3:G23)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>68</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>69</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>71</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>73</v>
       </c>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="F18" s="7">
         <f>SUM('RAYO VALLECANO'!F3:F25)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="8">
         <f>SUM('RAYO VALLECANO'!G3:G25)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>74</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>77</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>78</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>79</v>
       </c>
@@ -4419,14 +4419,14 @@
       </c>
       <c r="F24" s="7">
         <f>SUM('LALIGA FANTASY'!F3:F11)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" s="8">
         <f>SUM('LALIGA FANTASY'!G3:G11)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>81</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>83</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
         <v>84</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>85</v>
       </c>
@@ -4588,14 +4588,14 @@
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="76"/>
       <c r="B31" s="76"/>
       <c r="C31" s="76"/>
@@ -4604,7 +4604,7 @@
       <c r="F31" s="76"/>
       <c r="G31" s="76"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>86</v>
       </c>
@@ -4621,7 +4621,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4631,7 +4631,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>66</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>275</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>283</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -5134,7 +5134,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5144,7 +5144,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="85" t="s">
         <v>67</v>
       </c>
@@ -5155,7 +5155,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5192,13 +5192,15 @@
       <c r="E3" s="62">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
+      <c r="F3" s="63">
+        <v>1</v>
+      </c>
       <c r="G3" s="64">
         <f t="shared" ref="G3:G23" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5216,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5234,7 +5236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5252,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5274,7 +5276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5296,7 +5298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -5314,7 +5316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -5332,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>29</v>
       </c>
@@ -5354,7 +5356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
@@ -5372,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>33</v>
       </c>
@@ -5394,7 +5396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>37</v>
       </c>
@@ -5412,7 +5414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>39</v>
       </c>
@@ -5430,7 +5432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>41</v>
       </c>
@@ -5448,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>43</v>
       </c>
@@ -5466,7 +5468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>45</v>
       </c>
@@ -5484,7 +5486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>47</v>
       </c>
@@ -5504,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>49</v>
       </c>
@@ -5522,7 +5524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>51</v>
       </c>
@@ -5542,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>214</v>
       </c>
@@ -5560,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>53</v>
       </c>
@@ -5589,7 +5591,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5599,7 +5601,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="86" t="s">
         <v>68</v>
       </c>
@@ -5610,7 +5612,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5633,7 +5635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -5651,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -5669,7 +5671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -5687,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -5705,7 +5707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -5727,7 +5729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -5747,7 +5749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -5765,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -5783,7 +5785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -5805,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -5827,7 +5829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -5847,7 +5849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -5869,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -5891,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -5913,7 +5915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>159</v>
       </c>
@@ -5933,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>161</v>
       </c>
@@ -5951,7 +5953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -5969,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -5989,7 +5991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -6007,7 +6009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -6029,7 +6031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -6047,7 +6049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -6069,7 +6071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -6085,7 +6087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>111</v>
       </c>
@@ -6114,7 +6116,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6124,7 +6126,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="87" t="s">
         <v>69</v>
       </c>
@@ -6135,7 +6137,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6158,7 +6160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6180,7 +6182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6198,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6220,7 +6222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6238,7 +6240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6260,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6282,7 +6284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -6304,7 +6306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -6324,7 +6326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6346,7 +6348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6364,7 +6366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>343</v>
       </c>
@@ -6386,7 +6388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>345</v>
       </c>
@@ -6406,7 +6408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -6424,7 +6426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -6446,7 +6448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -6468,7 +6470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -6490,7 +6492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>351</v>
       </c>
@@ -6512,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>353</v>
       </c>
@@ -6532,7 +6534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>355</v>
       </c>
@@ -6552,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>357</v>
       </c>
@@ -6574,7 +6576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -6594,7 +6596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>360</v>
       </c>
@@ -6612,7 +6614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -6634,7 +6636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -6656,7 +6658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -6689,7 +6691,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -6699,7 +6701,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>70</v>
       </c>
@@ -6710,7 +6712,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6733,7 +6735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -6751,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -6769,7 +6771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -6787,7 +6789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -6809,7 +6811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -6831,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -6853,7 +6855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -6869,7 +6871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -6891,7 +6893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -6913,7 +6915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -6935,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -6953,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -6971,7 +6973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -6989,7 +6991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7011,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7031,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7053,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7071,7 +7073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7089,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -7111,7 +7113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>49</v>
       </c>
@@ -7133,7 +7135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -7155,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -7184,7 +7186,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7194,7 +7196,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>71</v>
       </c>
@@ -7205,7 +7207,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7228,7 +7230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7250,7 +7252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7272,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7290,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7308,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>19</v>
       </c>
@@ -7326,7 +7328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>21</v>
       </c>
@@ -7346,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>23</v>
       </c>
@@ -7364,7 +7366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7382,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7404,7 +7406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -7426,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -7444,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -7466,7 +7468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -7484,7 +7486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>254</v>
       </c>
@@ -7506,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>256</v>
       </c>
@@ -7522,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -7540,7 +7542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -7558,7 +7560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -7578,7 +7580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>165</v>
       </c>
@@ -7596,7 +7598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -7614,7 +7616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -7636,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -7658,7 +7660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -7687,7 +7689,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -7697,7 +7699,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="84" t="s">
         <v>72</v>
       </c>
@@ -7708,7 +7710,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7731,7 +7733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -7749,7 +7751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -7767,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -7785,7 +7787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -7807,7 +7809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -7825,7 +7827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -7841,7 +7843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -7859,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -7881,7 +7883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -7897,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -7915,7 +7917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -7937,7 +7939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -7959,7 +7961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -7981,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -8003,7 +8005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8021,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8043,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>131</v>
       </c>
@@ -8063,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>41</v>
       </c>
@@ -8083,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>43</v>
       </c>
@@ -8103,7 +8105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>283</v>
       </c>
@@ -8121,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>45</v>
       </c>
@@ -8139,7 +8141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>47</v>
       </c>
@@ -8161,7 +8163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -8179,7 +8181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>51</v>
       </c>
@@ -8197,7 +8199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>53</v>
       </c>
@@ -8230,7 +8232,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8240,7 +8242,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
         <v>73</v>
       </c>
@@ -8251,7 +8253,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8274,7 +8276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -8296,7 +8298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -8314,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -8336,7 +8338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -8354,7 +8356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -8376,7 +8378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -8394,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -8414,7 +8416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>339</v>
       </c>
@@ -8436,7 +8438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -8458,7 +8460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -8476,7 +8478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -8496,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -8514,7 +8516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>443</v>
       </c>
@@ -8536,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>445</v>
       </c>
@@ -8552,7 +8554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -8574,7 +8576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -8592,7 +8594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -8610,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -8628,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -8646,7 +8648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -8664,7 +8666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -8682,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -8700,7 +8702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -8714,10 +8716,12 @@
       <c r="E25" s="62">
         <v>1</v>
       </c>
-      <c r="F25" s="63"/>
+      <c r="F25" s="63">
+        <v>1</v>
+      </c>
       <c r="G25" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8731,7 +8735,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -8741,7 +8745,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>74</v>
       </c>
@@ -8752,7 +8756,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8775,7 +8779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -8793,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -8811,7 +8815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -8829,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -8851,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -8873,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -8891,7 +8895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -8909,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>27</v>
       </c>
@@ -8927,7 +8931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>29</v>
       </c>
@@ -8945,7 +8949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>31</v>
       </c>
@@ -8963,7 +8967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>33</v>
       </c>
@@ -8981,7 +8985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>37</v>
       </c>
@@ -8999,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>254</v>
       </c>
@@ -9021,7 +9025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52" t="s">
         <v>256</v>
       </c>
@@ -9037,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -9055,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -9077,7 +9081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -9099,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>47</v>
       </c>
@@ -9117,7 +9121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>49</v>
       </c>
@@ -9135,7 +9139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>51</v>
       </c>
@@ -9153,7 +9157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>53</v>
       </c>
@@ -9182,7 +9186,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9192,7 +9196,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="89" t="s">
         <v>75</v>
       </c>
@@ -9203,7 +9207,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9226,7 +9230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9248,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9266,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9284,7 +9288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9302,7 +9306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9320,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9340,7 +9344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>270</v>
       </c>
@@ -9358,7 +9362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -9380,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -9396,7 +9400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>224</v>
       </c>
@@ -9414,7 +9418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>123</v>
       </c>
@@ -9434,7 +9438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>125</v>
       </c>
@@ -9456,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>31</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>33</v>
       </c>
@@ -9494,7 +9498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -9516,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -9538,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -9558,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -9576,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -9594,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -9616,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -9638,7 +9642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -9658,7 +9662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -9676,7 +9680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -9709,7 +9713,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -9719,7 +9723,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="78" t="s">
         <v>59</v>
       </c>
@@ -9730,7 +9734,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9753,7 +9757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -9775,7 +9779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -9793,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -9815,7 +9819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -9833,7 +9837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -9851,7 +9855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -9869,7 +9873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -9887,7 +9891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -9903,7 +9907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -9921,7 +9925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -9939,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -9957,7 +9961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -9979,7 +9983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -10001,7 +10005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -10019,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -10037,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -10059,7 +10063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -10081,7 +10085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -10103,7 +10107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>106</v>
       </c>
@@ -10123,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>107</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -10163,7 +10167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -10185,7 +10189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>111</v>
       </c>
@@ -10212,7 +10216,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10222,7 +10226,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="90" t="s">
         <v>76</v>
       </c>
@@ -10233,7 +10237,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10256,7 +10260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10274,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10292,7 +10296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10310,7 +10314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10332,7 +10336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -10354,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>23</v>
       </c>
@@ -10376,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>25</v>
       </c>
@@ -10394,7 +10398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>149</v>
       </c>
@@ -10414,7 +10418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>95</v>
       </c>
@@ -10432,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>29</v>
       </c>
@@ -10454,7 +10458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>31</v>
       </c>
@@ -10472,7 +10476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>33</v>
       </c>
@@ -10490,7 +10494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>37</v>
       </c>
@@ -10508,7 +10512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>39</v>
       </c>
@@ -10526,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>41</v>
       </c>
@@ -10548,7 +10552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>43</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>45</v>
       </c>
@@ -10588,7 +10592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="52" t="s">
         <v>165</v>
       </c>
@@ -10606,7 +10610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>47</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>49</v>
       </c>
@@ -10642,7 +10646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>51</v>
       </c>
@@ -10658,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="52" t="s">
         <v>214</v>
       </c>
@@ -10676,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>520</v>
       </c>
@@ -10698,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>522</v>
       </c>
@@ -10729,7 +10733,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -10739,7 +10743,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="91" t="s">
         <v>77</v>
       </c>
@@ -10750,7 +10754,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10773,7 +10777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -10795,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -10817,7 +10821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -10839,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -10855,7 +10859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>17</v>
       </c>
@@ -10873,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -10895,7 +10899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>117</v>
       </c>
@@ -10915,7 +10919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>119</v>
       </c>
@@ -10933,7 +10937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>531</v>
       </c>
@@ -10951,7 +10955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>533</v>
       </c>
@@ -10971,7 +10975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>149</v>
       </c>
@@ -10991,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>95</v>
       </c>
@@ -11007,7 +11011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>29</v>
       </c>
@@ -11025,7 +11029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>31</v>
       </c>
@@ -11043,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>33</v>
       </c>
@@ -11061,7 +11065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>37</v>
       </c>
@@ -11079,7 +11083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>39</v>
       </c>
@@ -11101,7 +11105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>41</v>
       </c>
@@ -11119,7 +11123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>43</v>
       </c>
@@ -11137,7 +11141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>45</v>
       </c>
@@ -11159,7 +11163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>47</v>
       </c>
@@ -11177,7 +11181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -11195,7 +11199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -11213,7 +11217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -11246,7 +11250,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -11256,7 +11260,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="92" t="s">
         <v>549</v>
       </c>
@@ -11267,7 +11271,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
@@ -11290,7 +11294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>550</v>
       </c>
@@ -11308,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>552</v>
       </c>
@@ -11326,7 +11330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>554</v>
       </c>
@@ -11344,7 +11348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>556</v>
       </c>
@@ -11362,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>558</v>
       </c>
@@ -11380,7 +11384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>560</v>
       </c>
@@ -11398,7 +11402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>562</v>
       </c>
@@ -11416,7 +11420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>564</v>
       </c>
@@ -11434,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>566</v>
       </c>
@@ -11452,7 +11456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>568</v>
       </c>
@@ -11470,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>570</v>
       </c>
@@ -11488,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>572</v>
       </c>
@@ -11506,7 +11510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>574</v>
       </c>
@@ -11524,7 +11528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>576</v>
       </c>
@@ -11542,7 +11546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>578</v>
       </c>
@@ -11560,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>580</v>
       </c>
@@ -11578,7 +11582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>582</v>
       </c>
@@ -11596,7 +11600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>584</v>
       </c>
@@ -11614,7 +11618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>586</v>
       </c>
@@ -11632,7 +11636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>588</v>
       </c>
@@ -11650,7 +11654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>590</v>
       </c>
@@ -11668,7 +11672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>592</v>
       </c>
@@ -11686,7 +11690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>594</v>
       </c>
@@ -11704,7 +11708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>596</v>
       </c>
@@ -11722,7 +11726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>598</v>
       </c>
@@ -11740,7 +11744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="65" t="s">
         <v>600</v>
       </c>
@@ -11758,7 +11762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="58" t="s">
         <v>602</v>
       </c>
@@ -11776,7 +11780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="65" t="s">
         <v>604</v>
       </c>
@@ -11794,7 +11798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="58" t="s">
         <v>606</v>
       </c>
@@ -11812,7 +11816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="65" t="s">
         <v>608</v>
       </c>
@@ -11830,7 +11834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="58" t="s">
         <v>610</v>
       </c>
@@ -11848,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="65" t="s">
         <v>612</v>
       </c>
@@ -11866,7 +11870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="58" t="s">
         <v>614</v>
       </c>
@@ -11884,7 +11888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="65" t="s">
         <v>616</v>
       </c>
@@ -11902,7 +11906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="58" t="s">
         <v>618</v>
       </c>
@@ -11920,7 +11924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="65" t="s">
         <v>620</v>
       </c>
@@ -11938,7 +11942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="58" t="s">
         <v>622</v>
       </c>
@@ -11956,7 +11960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="65" t="s">
         <v>624</v>
       </c>
@@ -11974,7 +11978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="58" t="s">
         <v>626</v>
       </c>
@@ -11992,7 +11996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="65" t="s">
         <v>628</v>
       </c>
@@ -12021,7 +12025,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12031,8 +12035,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="93" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="76"/>
@@ -12042,7 +12046,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12065,7 +12069,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12083,7 +12087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12105,7 +12109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12127,7 +12131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12149,7 +12153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12171,7 +12175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12193,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12215,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12233,7 +12237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12251,7 +12255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12269,7 +12273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12287,7 +12291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12305,7 +12309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12323,7 +12327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12341,7 +12345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12370,7 +12374,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12380,8 +12384,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="94" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="76"/>
@@ -12391,7 +12395,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12414,7 +12418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12432,7 +12436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12454,7 +12458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12468,13 +12472,15 @@
       <c r="E5" s="22">
         <v>1</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="23">
+        <v>1</v>
+      </c>
       <c r="G5" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12492,7 +12498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12510,7 +12516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12528,7 +12534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12542,13 +12548,15 @@
       <c r="E9" s="22">
         <v>1</v>
       </c>
-      <c r="F9" s="23"/>
+      <c r="F9" s="23">
+        <v>1</v>
+      </c>
       <c r="G9" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12566,7 +12574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12599,7 +12607,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12609,8 +12617,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="95" t="s">
         <v>80</v>
       </c>
       <c r="B1" s="76"/>
@@ -12620,7 +12628,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12643,7 +12651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -12665,7 +12673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
@@ -12683,7 +12691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
@@ -12701,7 +12709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>15</v>
       </c>
@@ -12723,7 +12731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>90</v>
       </c>
@@ -12741,7 +12749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>23</v>
       </c>
@@ -12759,7 +12767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
@@ -12777,7 +12785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -12795,7 +12803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -12813,7 +12821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -12831,7 +12839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>33</v>
       </c>
@@ -12849,7 +12857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
@@ -12867,7 +12875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
@@ -12889,7 +12897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
@@ -12909,7 +12917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>43</v>
       </c>
@@ -12927,7 +12935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>45</v>
       </c>
@@ -12945,7 +12953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>47</v>
       </c>
@@ -12967,7 +12975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>49</v>
       </c>
@@ -12989,7 +12997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>51</v>
       </c>
@@ -13007,7 +13015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>53</v>
       </c>
@@ -13029,7 +13037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>670</v>
       </c>
@@ -13047,7 +13055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>672</v>
       </c>
@@ -13069,7 +13077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>674</v>
       </c>
@@ -13102,7 +13110,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13112,8 +13120,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="96" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="76"/>
@@ -13123,7 +13131,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13146,7 +13154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>676</v>
       </c>
@@ -13164,7 +13172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>677</v>
       </c>
@@ -13186,7 +13194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>678</v>
       </c>
@@ -13204,7 +13212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>679</v>
       </c>
@@ -13222,7 +13230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>680</v>
       </c>
@@ -13244,7 +13252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>681</v>
       </c>
@@ -13262,7 +13270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>682</v>
       </c>
@@ -13280,7 +13288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>683</v>
       </c>
@@ -13298,7 +13306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>684</v>
       </c>
@@ -13316,7 +13324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>685</v>
       </c>
@@ -13334,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>686</v>
       </c>
@@ -13352,7 +13360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>687</v>
       </c>
@@ -13374,7 +13382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>688</v>
       </c>
@@ -13392,7 +13400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>689</v>
       </c>
@@ -13410,7 +13418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>690</v>
       </c>
@@ -13428,7 +13436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>691</v>
       </c>
@@ -13446,7 +13454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>692</v>
       </c>
@@ -13468,7 +13476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>693</v>
       </c>
@@ -13486,7 +13494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>694</v>
       </c>
@@ -13504,7 +13512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>695</v>
       </c>
@@ -13522,7 +13530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>696</v>
       </c>
@@ -13544,7 +13552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>697</v>
       </c>
@@ -13562,7 +13570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>698</v>
       </c>
@@ -13591,7 +13599,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13601,8 +13609,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="97" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="76"/>
@@ -13612,7 +13620,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13635,7 +13643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>699</v>
       </c>
@@ -13651,7 +13659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>701</v>
       </c>
@@ -13667,7 +13675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>703</v>
       </c>
@@ -13683,7 +13691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>705</v>
       </c>
@@ -13699,7 +13707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>707</v>
       </c>
@@ -13715,7 +13723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>709</v>
       </c>
@@ -13731,7 +13739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>711</v>
       </c>
@@ -13747,7 +13755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>713</v>
       </c>
@@ -13763,7 +13771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>715</v>
       </c>
@@ -13781,7 +13789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>717</v>
       </c>
@@ -13797,7 +13805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>719</v>
       </c>
@@ -13813,7 +13821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>721</v>
       </c>
@@ -13829,7 +13837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>723</v>
       </c>
@@ -13847,7 +13855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>725</v>
       </c>
@@ -13863,7 +13871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>727</v>
       </c>
@@ -13890,7 +13898,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -13900,8 +13908,8 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="75" t="s">
         <v>729</v>
       </c>
       <c r="B1" s="76"/>
@@ -13911,7 +13919,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13934,7 +13942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>730</v>
       </c>
@@ -13952,7 +13960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>732</v>
       </c>
@@ -13970,7 +13978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>734</v>
       </c>
@@ -13988,7 +13996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>736</v>
       </c>
@@ -14010,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>738</v>
       </c>
@@ -14028,7 +14036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>740</v>
       </c>
@@ -14046,7 +14054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>742</v>
       </c>
@@ -14064,7 +14072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>744</v>
       </c>
@@ -14082,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>746</v>
       </c>
@@ -14104,7 +14112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>748</v>
       </c>
@@ -14126,7 +14134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>750</v>
       </c>
@@ -14144,7 +14152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>752</v>
       </c>
@@ -14162,7 +14170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>754</v>
       </c>
@@ -14180,7 +14188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>756</v>
       </c>
@@ -14198,7 +14206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>758</v>
       </c>
@@ -14216,7 +14224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>760</v>
       </c>
@@ -14238,7 +14246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>762</v>
       </c>
@@ -14256,7 +14264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>764</v>
       </c>
@@ -14274,7 +14282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>766</v>
       </c>
@@ -14292,7 +14300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>768</v>
       </c>
@@ -14310,7 +14318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>770</v>
       </c>
@@ -14332,7 +14340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>772</v>
       </c>
@@ -14350,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>774</v>
       </c>
@@ -14368,7 +14376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>776</v>
       </c>
@@ -14386,7 +14394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>778</v>
       </c>
@@ -14404,7 +14412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>780</v>
       </c>
@@ -14422,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>782</v>
       </c>
@@ -14440,7 +14448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>784</v>
       </c>
@@ -14462,7 +14470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>786</v>
       </c>
@@ -14480,7 +14488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>788</v>
       </c>
@@ -14498,7 +14506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>790</v>
       </c>
@@ -14516,7 +14524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>792</v>
       </c>
@@ -14534,7 +14542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>794</v>
       </c>
@@ -14552,7 +14560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>796</v>
       </c>
@@ -14570,7 +14578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>798</v>
       </c>
@@ -14592,7 +14600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>800</v>
       </c>
@@ -14614,7 +14622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>802</v>
       </c>
@@ -14632,7 +14640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>804</v>
       </c>
@@ -14650,7 +14658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
         <v>806</v>
       </c>
@@ -14668,7 +14676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>808</v>
       </c>
@@ -14686,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
         <v>810</v>
       </c>
@@ -14704,7 +14712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>812</v>
       </c>
@@ -14722,7 +14730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
         <v>814</v>
       </c>
@@ -14740,7 +14748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>816</v>
       </c>
@@ -14758,7 +14766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
         <v>818</v>
       </c>
@@ -14776,7 +14784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
         <v>820</v>
       </c>
@@ -14794,7 +14802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
         <v>822</v>
       </c>
@@ -14812,7 +14820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
         <v>824</v>
       </c>
@@ -14834,7 +14842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
         <v>826</v>
       </c>
@@ -14852,7 +14860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>828</v>
       </c>
@@ -14870,7 +14878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
         <v>830</v>
       </c>
@@ -14892,7 +14900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>832</v>
       </c>
@@ -14910,7 +14918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
         <v>834</v>
       </c>
@@ -14928,7 +14936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>836</v>
       </c>
@@ -14950,7 +14958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
         <v>838</v>
       </c>
@@ -14972,7 +14980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>840</v>
       </c>
@@ -14990,7 +14998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
         <v>842</v>
       </c>
@@ -15012,7 +15020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="25" t="s">
         <v>844</v>
       </c>
@@ -15030,7 +15038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>846</v>
       </c>
@@ -15048,7 +15056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="25" t="s">
         <v>848</v>
       </c>
@@ -15070,7 +15078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
         <v>850</v>
       </c>
@@ -15086,7 +15094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="25" t="s">
         <v>852</v>
       </c>
@@ -15106,7 +15114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>854</v>
       </c>
@@ -15122,7 +15130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="25" t="s">
         <v>856</v>
       </c>
@@ -15142,7 +15150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
         <v>858</v>
       </c>
@@ -15162,7 +15170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
         <v>860</v>
       </c>
@@ -15178,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
         <v>862</v>
       </c>
@@ -15196,7 +15204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
         <v>864</v>
       </c>
@@ -15212,7 +15220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
         <v>866</v>
       </c>
@@ -15228,7 +15236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
         <v>868</v>
       </c>
@@ -15248,7 +15256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
         <v>870</v>
       </c>
@@ -15264,7 +15272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
         <v>872</v>
       </c>
@@ -15284,7 +15292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
         <v>874</v>
       </c>
@@ -15300,7 +15308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="25" t="s">
         <v>876</v>
       </c>
@@ -15316,7 +15324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
         <v>878</v>
       </c>
@@ -15332,7 +15340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="25" t="s">
         <v>880</v>
       </c>
@@ -15348,7 +15356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
         <v>882</v>
       </c>
@@ -15366,7 +15374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="25" t="s">
         <v>884</v>
       </c>
@@ -15382,7 +15390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
         <v>886</v>
       </c>
@@ -15402,7 +15410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="25" t="s">
         <v>888</v>
       </c>
@@ -15433,7 +15441,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15443,7 +15451,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>60</v>
       </c>
@@ -15454,7 +15462,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15477,7 +15485,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -15495,7 +15503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>11</v>
       </c>
@@ -15515,7 +15523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
@@ -15533,7 +15541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>15</v>
       </c>
@@ -15555,7 +15563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>90</v>
       </c>
@@ -15573,7 +15581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>117</v>
       </c>
@@ -15589,7 +15597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>119</v>
       </c>
@@ -15611,7 +15619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -15633,7 +15641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -15655,7 +15663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -15673,7 +15681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -15689,7 +15697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -15711,7 +15719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -15733,7 +15741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -15755,7 +15763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>39</v>
       </c>
@@ -15771,7 +15779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>131</v>
       </c>
@@ -15789,7 +15797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -15807,7 +15815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -15829,7 +15837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -15851,7 +15859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>136</v>
       </c>
@@ -15871,7 +15879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>138</v>
       </c>
@@ -15893,7 +15901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>49</v>
       </c>
@@ -15915,7 +15923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>51</v>
       </c>
@@ -15937,7 +15945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>53</v>
       </c>
@@ -15970,7 +15978,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -15980,7 +15988,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>61</v>
       </c>
@@ -15991,7 +15999,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16014,7 +16022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16032,7 +16040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16050,7 +16058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16068,7 +16076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16086,7 +16094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16104,7 +16112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -16120,7 +16128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -16142,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>149</v>
       </c>
@@ -16160,7 +16168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -16180,7 +16188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16198,7 +16206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16218,7 +16226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>154</v>
       </c>
@@ -16236,7 +16244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -16258,7 +16266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -16280,7 +16288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -16302,7 +16310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>159</v>
       </c>
@@ -16324,7 +16332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>161</v>
       </c>
@@ -16344,7 +16352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -16366,7 +16374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -16386,7 +16394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>165</v>
       </c>
@@ -16404,7 +16412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>47</v>
       </c>
@@ -16422,7 +16430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>49</v>
       </c>
@@ -16440,7 +16448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>51</v>
       </c>
@@ -16458,7 +16466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -16487,7 +16495,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16497,7 +16505,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="80" t="s">
         <v>62</v>
       </c>
@@ -16508,7 +16516,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16531,7 +16539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -16549,7 +16557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -16571,7 +16579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -16589,7 +16597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -16611,7 +16619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -16629,7 +16637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>117</v>
       </c>
@@ -16649,7 +16657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>119</v>
       </c>
@@ -16667,7 +16675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>25</v>
       </c>
@@ -16685,7 +16693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>27</v>
       </c>
@@ -16703,7 +16711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>29</v>
       </c>
@@ -16725,7 +16733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -16747,7 +16755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -16762,14 +16770,14 @@
         <v>2</v>
       </c>
       <c r="F14" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -16791,7 +16799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -16809,7 +16817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -16827,7 +16835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>43</v>
       </c>
@@ -16845,7 +16853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>45</v>
       </c>
@@ -16863,7 +16871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>47</v>
       </c>
@@ -16881,7 +16889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>49</v>
       </c>
@@ -16901,7 +16909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>188</v>
       </c>
@@ -16919,7 +16927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>51</v>
       </c>
@@ -16937,7 +16945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
@@ -16966,7 +16974,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -16976,7 +16984,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
@@ -16987,7 +16995,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17010,7 +17018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17028,7 +17036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17046,7 +17054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17064,7 +17072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17080,7 +17088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>17</v>
       </c>
@@ -17098,7 +17106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>19</v>
       </c>
@@ -17114,7 +17122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>21</v>
       </c>
@@ -17136,7 +17144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>23</v>
       </c>
@@ -17154,7 +17162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>25</v>
       </c>
@@ -17172,7 +17180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>27</v>
       </c>
@@ -17194,7 +17202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>29</v>
       </c>
@@ -17212,7 +17220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -17230,7 +17238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -17250,7 +17258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
@@ -17268,7 +17276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>37</v>
       </c>
@@ -17286,7 +17294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>39</v>
       </c>
@@ -17304,7 +17312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
@@ -17326,7 +17334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -17348,7 +17356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -17370,7 +17378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -17392,7 +17400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -17414,7 +17422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17432,7 +17440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -17461,7 +17469,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17471,7 +17479,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="82" t="s">
         <v>63</v>
       </c>
@@ -17482,7 +17490,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17505,7 +17513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -17523,7 +17531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -17541,7 +17549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -17559,7 +17567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -17581,7 +17589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -17599,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -17617,7 +17625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -17639,7 +17647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -17657,7 +17665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>123</v>
       </c>
@@ -17675,7 +17683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>125</v>
       </c>
@@ -17695,7 +17703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>31</v>
       </c>
@@ -17713,7 +17721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
@@ -17731,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>37</v>
       </c>
@@ -17753,7 +17761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>39</v>
       </c>
@@ -17775,7 +17783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>41</v>
       </c>
@@ -17797,7 +17805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>206</v>
       </c>
@@ -17813,7 +17821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>43</v>
       </c>
@@ -17829,7 +17837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>45</v>
       </c>
@@ -17847,7 +17855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>47</v>
       </c>
@@ -17865,7 +17873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>106</v>
       </c>
@@ -17887,7 +17895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>107</v>
       </c>
@@ -17903,7 +17911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -17925,7 +17933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>214</v>
       </c>
@@ -17941,7 +17949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
@@ -17970,7 +17978,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -17980,7 +17988,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83" t="s">
         <v>64</v>
       </c>
@@ -17991,7 +17999,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18014,7 +18022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>8</v>
       </c>
@@ -18036,7 +18044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>11</v>
       </c>
@@ -18054,7 +18062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>13</v>
       </c>
@@ -18072,7 +18080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>15</v>
       </c>
@@ -18090,7 +18098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>90</v>
       </c>
@@ -18108,7 +18116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
         <v>23</v>
       </c>
@@ -18126,7 +18134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>25</v>
       </c>
@@ -18148,7 +18156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="65" t="s">
         <v>27</v>
       </c>
@@ -18170,7 +18178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>224</v>
       </c>
@@ -18186,7 +18194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="65" t="s">
         <v>123</v>
       </c>
@@ -18208,7 +18216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>125</v>
       </c>
@@ -18228,7 +18236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="65" t="s">
         <v>31</v>
       </c>
@@ -18246,7 +18254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>33</v>
       </c>
@@ -18264,7 +18272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>37</v>
       </c>
@@ -18282,7 +18290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>39</v>
       </c>
@@ -18300,7 +18308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>41</v>
       </c>
@@ -18318,7 +18326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="58" t="s">
         <v>206</v>
       </c>
@@ -18334,7 +18342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="65" t="s">
         <v>43</v>
       </c>
@@ -18352,7 +18360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="58" t="s">
         <v>45</v>
       </c>
@@ -18374,7 +18382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
         <v>47</v>
       </c>
@@ -18392,7 +18400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>49</v>
       </c>
@@ -18414,7 +18422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="65" t="s">
         <v>51</v>
       </c>
@@ -18432,7 +18440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>53</v>
       </c>
@@ -18465,7 +18473,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -18475,7 +18483,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="84" t="s">
         <v>65</v>
       </c>
@@ -18486,7 +18494,7 @@
       <c r="F1" s="76"/>
       <c r="G1" s="76"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18509,7 +18517,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
         <v>8</v>
       </c>
@@ -18527,7 +18535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="52" t="s">
         <v>11</v>
       </c>
@@ -18543,7 +18551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>241</v>
       </c>
@@ -18561,7 +18569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>13</v>
       </c>
@@ -18583,7 +18591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>15</v>
       </c>
@@ -18601,7 +18609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>90</v>
       </c>
@@ -18617,7 +18625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>23</v>
       </c>
@@ -18635,7 +18643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>25</v>
       </c>
@@ -18653,7 +18661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>27</v>
       </c>
@@ -18669,7 +18677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>123</v>
       </c>
@@ -18689,7 +18697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>125</v>
       </c>
@@ -18707,7 +18715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>31</v>
       </c>
@@ -18729,7 +18737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>33</v>
       </c>
@@ -18751,7 +18759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>37</v>
       </c>
@@ -18769,7 +18777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
@@ -18791,7 +18799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>256</v>
       </c>
@@ -18807,7 +18815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -18829,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>43</v>
       </c>
@@ -18851,7 +18859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>45</v>
       </c>
@@ -18873,7 +18881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>47</v>
       </c>
@@ -18891,7 +18899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>49</v>
       </c>
@@ -18909,7 +18917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>51</v>
       </c>
@@ -18931,7 +18939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>53</v>
       </c>

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20004C6A-6932-4FDE-BEC0-9525278AAB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A187C0-109C-4007-B9C1-A531F7ACC88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3411,9 +3411,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3465,6 +3462,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="F4" s="7">
         <f>SUM('ATHLETIC CLUB'!F3:F26)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="8">
         <f>SUM('ATHLETIC CLUB'!G3:G26)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4055,11 +4055,11 @@
       </c>
       <c r="F11" s="7">
         <f>SUM('RCD ESPANYOL'!F3:F25)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="8">
         <f>SUM('RCD ESPANYOL'!G3:G25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4167,11 +4167,11 @@
       </c>
       <c r="F15" s="7">
         <f>SUM('MÁLAGA CF'!F3:F24)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" s="8">
         <f>SUM('MÁLAGA CF'!G3:G24)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4191,15 +4191,15 @@
       </c>
       <c r="E16" s="6">
         <f>SUMIF('CA OSASUNA'!E3:E25,"&gt;"&amp;0,'CA OSASUNA'!E3:E25)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="7">
         <f>SUM('CA OSASUNA'!F3:F25)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="8">
         <f>SUM('CA OSASUNA'!G3:G25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4447,11 +4447,11 @@
       </c>
       <c r="F25" s="7">
         <f>SUM('DRAFT 23'!F3:F25)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="8">
         <f>SUM('DRAFT 23'!G3:G25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4584,15 +4584,15 @@
       </c>
       <c r="E30" s="15">
         <f t="shared" si="0"/>
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F30" s="16">
         <f t="shared" si="0"/>
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -4632,7 +4632,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="76"/>
@@ -5098,11 +5098,11 @@
         <v>2</v>
       </c>
       <c r="F24" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5145,7 +5145,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="76"/>
@@ -5602,7 +5602,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="85" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="76"/>
@@ -6127,7 +6127,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="76"/>
@@ -6702,7 +6702,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="76"/>
@@ -7128,11 +7128,11 @@
         <v>2</v>
       </c>
       <c r="F22" s="63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7242,10 +7242,10 @@
       </c>
       <c r="D3" s="61"/>
       <c r="E3" s="62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="64">
         <f t="shared" ref="G3:G25" si="0">MAX(0,IF(E3="",0,E3)-IF(F3="",0,F3))</f>
@@ -7399,11 +7399,11 @@
         <v>3</v>
       </c>
       <c r="F11" s="63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="64">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7700,7 +7700,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="83" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="76"/>
@@ -8243,7 +8243,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>73</v>
       </c>
       <c r="B1" s="76"/>
@@ -8746,7 +8746,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="76"/>
@@ -9197,7 +9197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="88" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="76"/>
@@ -10227,7 +10227,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="89" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="76"/>
@@ -10744,7 +10744,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="90" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="76"/>
@@ -11261,7 +11261,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="91" t="s">
         <v>549</v>
       </c>
       <c r="B1" s="76"/>
@@ -12036,7 +12036,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="92" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="76"/>
@@ -12385,7 +12385,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="93" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="76"/>
@@ -12618,7 +12618,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="94" t="s">
         <v>80</v>
       </c>
       <c r="B1" s="76"/>
@@ -12911,10 +12911,12 @@
       <c r="E16" s="22">
         <v>1</v>
       </c>
-      <c r="F16" s="23"/>
+      <c r="F16" s="23">
+        <v>1</v>
+      </c>
       <c r="G16" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -13121,7 +13123,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="76"/>
@@ -13610,7 +13612,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="96" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="76"/>
@@ -13909,7 +13911,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="97" t="s">
         <v>729</v>
       </c>
       <c r="B1" s="76"/>
@@ -15517,10 +15519,12 @@
       <c r="E4" s="38">
         <v>1</v>
       </c>
-      <c r="F4" s="39"/>
+      <c r="F4" s="39">
+        <v>1</v>
+      </c>
       <c r="G4" s="40">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -16506,7 +16510,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="75" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="76"/>
@@ -16985,7 +16989,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="76"/>
@@ -17480,7 +17484,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="76"/>
@@ -17989,7 +17993,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="76"/>
@@ -18484,7 +18488,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="83" t="s">
         <v>65</v>
       </c>
       <c r="B1" s="76"/>
